--- a/job-classification-kb/不合理清單_職類校正.xlsx
+++ b/job-classification-kb/不合理清單_職類校正.xlsx
@@ -34,7 +34,7 @@
       <strike val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -71,6 +71,16 @@
         <bgColor rgb="FFFFA500"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFA500"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -84,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -101,6 +111,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -466,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1073"/>
+  <dimension ref="A1:M1073"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -552,6 +564,11 @@
           <t>現有5</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>建議1</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -585,7 +602,7 @@
           <t>招生業務主管</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="8" t="inlineStr">
         <is>
           <t>經營管理主管</t>
         </is>
@@ -598,6 +615,11 @@
       <c r="J2" s="7" t="inlineStr">
         <is>
           <t>市場調查／分析人員</t>
+        </is>
+      </c>
+      <c r="M2" s="9" t="inlineStr">
+        <is>
+          <t>國內業務主管</t>
         </is>
       </c>
     </row>
@@ -633,7 +655,7 @@
           <t>工廠管理儲備幹部</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>經營管理主管</t>
         </is>
@@ -656,6 +678,11 @@
       <c r="L3" t="inlineStr">
         <is>
           <t>製程主管</t>
+        </is>
+      </c>
+      <c r="M3" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -691,9 +718,14 @@
           <t>停車場管理儲備幹部</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>經營管理主管</t>
+        </is>
+      </c>
+      <c r="M4" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -729,7 +761,7 @@
           <t>經營儲備幹部（市場開發/業務管理）</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>經營管理主管</t>
         </is>
@@ -742,6 +774,11 @@
       <c r="J5" s="7" t="inlineStr">
         <is>
           <t>產品經理</t>
+        </is>
+      </c>
+      <c r="M5" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -878,7 +915,7 @@
           <t>勤務儲備幹部</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>經營管理主管</t>
         </is>
@@ -891,6 +928,11 @@
       <c r="J8" t="inlineStr">
         <is>
           <t>保全人員／警衛</t>
+        </is>
+      </c>
+      <c r="M8" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -964,7 +1006,7 @@
           <t>業務助理</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>特別助理</t>
         </is>
@@ -972,6 +1014,11 @@
       <c r="I10" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M10" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1054,7 @@
           <t>主管司機</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>特別助理</t>
         </is>
@@ -1015,6 +1062,11 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>小客車／小貨車司機</t>
+        </is>
+      </c>
+      <c r="M11" s="9" t="inlineStr">
+        <is>
+          <t>主管駕駛</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1246,7 @@
           <t>主管司機(隨扈司機)</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>特別助理</t>
         </is>
@@ -1207,6 +1259,11 @@
       <c r="J15" s="7" t="inlineStr">
         <is>
           <t>隨扈／安全人員</t>
+        </is>
+      </c>
+      <c r="M15" s="9" t="inlineStr">
+        <is>
+          <t>主管駕駛</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1385,7 @@
           <t>業務助理</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>儲備幹部</t>
         </is>
@@ -1336,6 +1393,11 @@
       <c r="I18" s="7" t="inlineStr">
         <is>
           <t>基層管理幹部</t>
+        </is>
+      </c>
+      <c r="M18" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1529,7 @@
           <t>採購人員</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>人事／人力資源主管</t>
         </is>
@@ -1480,6 +1542,11 @@
       <c r="J21" t="inlineStr">
         <is>
           <t>倉管／物料管理員</t>
+        </is>
+      </c>
+      <c r="M21" s="9" t="inlineStr">
+        <is>
+          <t>採購人員</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1582,7 @@
           <t>居服組長</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>人事／人力資源主管</t>
         </is>
@@ -1538,6 +1605,11 @@
       <c r="L22" t="inlineStr">
         <is>
           <t>居家服務督導員</t>
+        </is>
+      </c>
+      <c r="M22" s="9" t="inlineStr">
+        <is>
+          <t>照顧服務／指導員</t>
         </is>
       </c>
     </row>
@@ -1573,9 +1645,14 @@
           <t>知名遊戲代理商－打造超級APP-遊戲營運PM</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>人事／人力資源主管</t>
+        </is>
+      </c>
+      <c r="M23" s="9" t="inlineStr">
+        <is>
+          <t>產品經理</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1736,7 @@
           <t>環保清潔幹部</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>人事／人力資源主管</t>
         </is>
@@ -1672,6 +1749,11 @@
       <c r="J25" t="inlineStr">
         <is>
           <t>基層管理幹部</t>
+        </is>
+      </c>
+      <c r="M25" s="9" t="inlineStr">
+        <is>
+          <t>清潔／資源回收人員</t>
         </is>
       </c>
     </row>
@@ -1755,7 +1837,7 @@
           <t>儲備幹部 { 台南市 }</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>人事／人力資源主管</t>
         </is>
@@ -1768,6 +1850,11 @@
       <c r="J27" t="inlineStr">
         <is>
           <t>總務人員</t>
+        </is>
+      </c>
+      <c r="M27" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2252,7 @@
           <t>獵才主管/儲備幹部</t>
         </is>
       </c>
-      <c r="H37" s="7" t="inlineStr">
+      <c r="H37" s="8" t="inlineStr">
         <is>
           <t>人事／人力資源專員</t>
         </is>
@@ -2173,6 +2260,11 @@
       <c r="I37" s="7" t="inlineStr">
         <is>
           <t>人事／人力資源主管</t>
+        </is>
+      </c>
+      <c r="M37" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2300,7 @@
           <t>人資儲備幹部</t>
         </is>
       </c>
-      <c r="H38" s="7" t="inlineStr">
+      <c r="H38" s="8" t="inlineStr">
         <is>
           <t>人事／人力資源專員</t>
         </is>
@@ -2221,6 +2313,11 @@
       <c r="J38" s="7" t="inlineStr">
         <is>
           <t>教育訓練人員</t>
+        </is>
+      </c>
+      <c r="M38" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2396,7 @@
           <t>儲備幹部(台北忠孝分院)</t>
         </is>
       </c>
-      <c r="H40" s="7" t="inlineStr">
+      <c r="H40" s="8" t="inlineStr">
         <is>
           <t>人事／人力資源專員</t>
         </is>
@@ -2307,6 +2404,11 @@
       <c r="I40" t="inlineStr">
         <is>
           <t>經營管理主管</t>
+        </is>
+      </c>
+      <c r="M40" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2444,7 @@
           <t>儲備幹部(台中公益分院)</t>
         </is>
       </c>
-      <c r="H41" s="7" t="inlineStr">
+      <c r="H41" s="8" t="inlineStr">
         <is>
           <t>人事／人力資源專員</t>
         </is>
@@ -2350,6 +2452,11 @@
       <c r="I41" t="inlineStr">
         <is>
           <t>經營管理主管</t>
+        </is>
+      </c>
+      <c r="M41" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2535,7 @@
           <t>左營區●業務專員 回line 、po文 就有業績 無上限任你領~</t>
         </is>
       </c>
-      <c r="H43" s="7" t="inlineStr">
+      <c r="H43" s="8" t="inlineStr">
         <is>
           <t>人事／人力資源專員</t>
         </is>
@@ -2441,6 +2548,11 @@
       <c r="J43" t="inlineStr">
         <is>
           <t>電話行銷人員</t>
+        </is>
+      </c>
+      <c r="M43" s="9" t="inlineStr">
+        <is>
+          <t>國內業務人員</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2588,7 @@
           <t>免學歷挑戰高薪⭐正職好同事在這裡⭐業務助理⭐人資助理⭐招募助理⭐內勤免外出⭐</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H44" s="8" t="inlineStr">
         <is>
           <t>人事／人力資源專員</t>
         </is>
@@ -2489,6 +2601,11 @@
       <c r="J44" s="7" t="inlineStr">
         <is>
           <t>電話客服人員</t>
+        </is>
+      </c>
+      <c r="M44" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2924,7 @@
           <t>✨閃亮亮【召募辦公室業務人員】+見紅休+獎金多多+周休二日</t>
         </is>
       </c>
-      <c r="H51" s="7" t="inlineStr">
+      <c r="H51" s="8" t="inlineStr">
         <is>
           <t>人事／人力資源專員</t>
         </is>
@@ -2820,6 +2937,11 @@
       <c r="J51" s="7" t="inlineStr">
         <is>
           <t>客服人員</t>
+        </is>
+      </c>
+      <c r="M51" s="9" t="inlineStr">
+        <is>
+          <t>國內業務人員</t>
         </is>
       </c>
     </row>
@@ -2903,7 +3025,7 @@
           <t>行政管理儲備幹部</t>
         </is>
       </c>
-      <c r="H53" s="7" t="inlineStr">
+      <c r="H53" s="8" t="inlineStr">
         <is>
           <t>人事／人力資源專員</t>
         </is>
@@ -2916,6 +3038,11 @@
       <c r="J53" s="7" t="inlineStr">
         <is>
           <t>行政主管</t>
+        </is>
+      </c>
+      <c r="M53" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -2999,7 +3126,7 @@
           <t>招募專員/儲備幹部/獎金制度/周休二日</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H55" s="8" t="inlineStr">
         <is>
           <t>人事／人力資源專員</t>
         </is>
@@ -3007,6 +3134,11 @@
       <c r="I55" t="inlineStr">
         <is>
           <t>人力／外勞仲介</t>
+        </is>
+      </c>
+      <c r="M55" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3356,7 @@
           <t>人資專員(儲備幹部)</t>
         </is>
       </c>
-      <c r="H60" s="7" t="inlineStr">
+      <c r="H60" s="8" t="inlineStr">
         <is>
           <t>人事／人力資源專員</t>
         </is>
@@ -3232,6 +3364,11 @@
       <c r="I60" s="7" t="inlineStr">
         <is>
           <t>教育訓練人員</t>
+        </is>
+      </c>
+      <c r="M60" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3452,7 @@
           <t>管理部_資深專員( 儲備主任)</t>
         </is>
       </c>
-      <c r="H62" s="7" t="inlineStr">
+      <c r="H62" s="8" t="inlineStr">
         <is>
           <t>人事／人力資源專員</t>
         </is>
@@ -3328,6 +3465,11 @@
       <c r="J62" t="inlineStr">
         <is>
           <t>總務主管</t>
+        </is>
+      </c>
+      <c r="M62" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -3411,9 +3553,14 @@
           <t>新北林口區-印尼雙語業務人員 Sales Lapangan</t>
         </is>
       </c>
-      <c r="H64" s="7" t="inlineStr">
+      <c r="H64" s="8" t="inlineStr">
         <is>
           <t>人力／外勞仲介</t>
+        </is>
+      </c>
+      <c r="M64" s="9" t="inlineStr">
+        <is>
+          <t>國內業務人員</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3639,7 @@
           <t>駐區經營業務主管(新北全區)</t>
         </is>
       </c>
-      <c r="H66" s="7" t="inlineStr">
+      <c r="H66" s="8" t="inlineStr">
         <is>
           <t>人力／外勞仲介</t>
         </is>
@@ -3500,6 +3647,11 @@
       <c r="I66" t="inlineStr">
         <is>
           <t>經營管理主管</t>
+        </is>
+      </c>
+      <c r="M66" s="9" t="inlineStr">
+        <is>
+          <t>國內業務主管</t>
         </is>
       </c>
     </row>
@@ -3535,9 +3687,14 @@
           <t>台中南區-印尼雙語業務人員 Sales Lapangan</t>
         </is>
       </c>
-      <c r="H67" s="7" t="inlineStr">
+      <c r="H67" s="8" t="inlineStr">
         <is>
           <t>人力／外勞仲介</t>
+        </is>
+      </c>
+      <c r="M67" s="9" t="inlineStr">
+        <is>
+          <t>國內業務人員</t>
         </is>
       </c>
     </row>
@@ -3573,7 +3730,7 @@
           <t>會計行政人員</t>
         </is>
       </c>
-      <c r="H68" s="7" t="inlineStr">
+      <c r="H68" s="8" t="inlineStr">
         <is>
           <t>人力／外勞仲介</t>
         </is>
@@ -3586,6 +3743,11 @@
       <c r="J68" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M68" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -3674,9 +3836,14 @@
           <t>新北林口區-印尼雙語電話行銷人員 Sales Kantor</t>
         </is>
       </c>
-      <c r="H70" s="7" t="inlineStr">
+      <c r="H70" s="8" t="inlineStr">
         <is>
           <t>人力／外勞仲介</t>
+        </is>
+      </c>
+      <c r="M70" s="9" t="inlineStr">
+        <is>
+          <t>國內業務人員</t>
         </is>
       </c>
     </row>
@@ -3874,9 +4041,14 @@
           <t>雲林虎尾鎮-印尼雙語電話行銷人員 Sales Kantor</t>
         </is>
       </c>
-      <c r="H75" s="7" t="inlineStr">
+      <c r="H75" s="8" t="inlineStr">
         <is>
           <t>人力／外勞仲介</t>
+        </is>
+      </c>
+      <c r="M75" s="9" t="inlineStr">
+        <is>
+          <t>國內業務人員</t>
         </is>
       </c>
     </row>
@@ -3955,7 +4127,7 @@
           <t>印尼業務專員/翻譯/行銷專員/業務</t>
         </is>
       </c>
-      <c r="H77" s="7" t="inlineStr">
+      <c r="H77" s="8" t="inlineStr">
         <is>
           <t>人力／外勞仲介</t>
         </is>
@@ -3963,6 +4135,11 @@
       <c r="I77" s="7" t="inlineStr">
         <is>
           <t>客服人員</t>
+        </is>
+      </c>
+      <c r="M77" s="9" t="inlineStr">
+        <is>
+          <t>國內業務人員</t>
         </is>
       </c>
     </row>
@@ -4213,9 +4390,14 @@
           <t>高雄苓雅區-印尼雙語業務人員 Sales Lapangan</t>
         </is>
       </c>
-      <c r="H83" s="7" t="inlineStr">
+      <c r="H83" s="8" t="inlineStr">
         <is>
           <t>人力／外勞仲介</t>
+        </is>
+      </c>
+      <c r="M83" s="9" t="inlineStr">
+        <is>
+          <t>國內業務人員</t>
         </is>
       </c>
     </row>
@@ -4294,9 +4476,14 @@
           <t>儲備幹部</t>
         </is>
       </c>
-      <c r="H85" s="7" t="inlineStr">
+      <c r="H85" s="8" t="inlineStr">
         <is>
           <t>人力／外勞仲介</t>
+        </is>
+      </c>
+      <c r="M85" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -4332,7 +4519,7 @@
           <t>高雄-集團行銷業務專員(可培訓.保障底薪+獎金)TCM</t>
         </is>
       </c>
-      <c r="H86" s="7" t="inlineStr">
+      <c r="H86" s="8" t="inlineStr">
         <is>
           <t>人力／外勞仲介</t>
         </is>
@@ -4345,6 +4532,11 @@
       <c r="J86" t="inlineStr">
         <is>
           <t>通路開發人員</t>
+        </is>
+      </c>
+      <c r="M86" s="9" t="inlineStr">
+        <is>
+          <t>國內業務人員</t>
         </is>
       </c>
     </row>
@@ -4380,9 +4572,14 @@
           <t>雲林虎尾鎮-印尼雙語業務人員 Sales Lapangan</t>
         </is>
       </c>
-      <c r="H87" s="7" t="inlineStr">
+      <c r="H87" s="8" t="inlineStr">
         <is>
           <t>人力／外勞仲介</t>
+        </is>
+      </c>
+      <c r="M87" s="9" t="inlineStr">
+        <is>
+          <t>國內業務人員</t>
         </is>
       </c>
     </row>
@@ -4499,7 +4696,7 @@
           <t>【台中】集團內部正職業務儲備幹部</t>
         </is>
       </c>
-      <c r="H90" s="7" t="inlineStr">
+      <c r="H90" s="8" t="inlineStr">
         <is>
           <t>人力／外勞仲介</t>
         </is>
@@ -4512,6 +4709,11 @@
       <c r="J90" s="7" t="inlineStr">
         <is>
           <t>通路開發人員</t>
+        </is>
+      </c>
+      <c r="M90" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -4547,9 +4749,14 @@
           <t>業務人員-中壢</t>
         </is>
       </c>
-      <c r="H91" s="7" t="inlineStr">
+      <c r="H91" s="8" t="inlineStr">
         <is>
           <t>人力／外勞仲介</t>
+        </is>
+      </c>
+      <c r="M91" s="9" t="inlineStr">
+        <is>
+          <t>國內業務人員</t>
         </is>
       </c>
     </row>
@@ -4585,9 +4792,14 @@
           <t>高雄苓雅區-印尼雙語電話行銷人員 Sales Kantor</t>
         </is>
       </c>
-      <c r="H92" s="7" t="inlineStr">
+      <c r="H92" s="8" t="inlineStr">
         <is>
           <t>人力／外勞仲介</t>
+        </is>
+      </c>
+      <c r="M92" s="9" t="inlineStr">
+        <is>
+          <t>國內業務人員</t>
         </is>
       </c>
     </row>
@@ -4666,9 +4878,14 @@
           <t>業務助理</t>
         </is>
       </c>
-      <c r="H94" s="7" t="inlineStr">
+      <c r="H94" s="8" t="inlineStr">
         <is>
           <t>人力／外勞仲介</t>
+        </is>
+      </c>
+      <c r="M94" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -4704,9 +4921,14 @@
           <t>(高雄)業務人員(無經驗可,高獎金)</t>
         </is>
       </c>
-      <c r="H95" s="7" t="inlineStr">
+      <c r="H95" s="8" t="inlineStr">
         <is>
           <t>人力／外勞仲介</t>
+        </is>
+      </c>
+      <c r="M95" s="9" t="inlineStr">
+        <is>
+          <t>國內業務人員</t>
         </is>
       </c>
     </row>
@@ -4742,9 +4964,14 @@
           <t>電話行銷人員(內部徵才)</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="H96" s="8" t="inlineStr">
         <is>
           <t>人力／外勞仲介</t>
+        </is>
+      </c>
+      <c r="M96" s="9" t="inlineStr">
+        <is>
+          <t>國內業務人員</t>
         </is>
       </c>
     </row>
@@ -4828,9 +5055,14 @@
           <t>📢 誠徵【泰語翻譯人員兼業務助理】📢</t>
         </is>
       </c>
-      <c r="H98" s="7" t="inlineStr">
+      <c r="H98" s="8" t="inlineStr">
         <is>
           <t>人力／外勞仲介</t>
+        </is>
+      </c>
+      <c r="M98" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -5205,7 +5437,7 @@
           <t>＜儲備＞按摩區經理(大台中地區)</t>
         </is>
       </c>
-      <c r="H107" s="7" t="inlineStr">
+      <c r="H107" s="8" t="inlineStr">
         <is>
           <t>教育訓練人員</t>
         </is>
@@ -5218,6 +5450,11 @@
       <c r="J107" s="7" t="inlineStr">
         <is>
           <t>店長／門市管理人員</t>
+        </is>
+      </c>
+      <c r="M107" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5490,7 @@
           <t>＜儲備＞按摩區經理(大台南地區)</t>
         </is>
       </c>
-      <c r="H108" s="7" t="inlineStr">
+      <c r="H108" s="8" t="inlineStr">
         <is>
           <t>教育訓練人員</t>
         </is>
@@ -5266,6 +5503,11 @@
       <c r="J108" s="7" t="inlineStr">
         <is>
           <t>店長／門市管理人員</t>
+        </is>
+      </c>
+      <c r="M108" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -5301,7 +5543,7 @@
           <t>＜儲備＞按摩區經理(大高雄地區)</t>
         </is>
       </c>
-      <c r="H109" s="7" t="inlineStr">
+      <c r="H109" s="8" t="inlineStr">
         <is>
           <t>教育訓練人員</t>
         </is>
@@ -5314,6 +5556,11 @@
       <c r="J109" s="7" t="inlineStr">
         <is>
           <t>店長／門市管理人員</t>
+        </is>
+      </c>
+      <c r="M109" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -5349,7 +5596,7 @@
           <t>總部-早午餐培訓儲備主管【需出差、具備餐飲管理經驗】台北/需自備車輛</t>
         </is>
       </c>
-      <c r="H110" s="7" t="inlineStr">
+      <c r="H110" s="8" t="inlineStr">
         <is>
           <t>教育訓練人員</t>
         </is>
@@ -5362,6 +5609,11 @@
       <c r="J110" t="inlineStr">
         <is>
           <t>餐飲服務人員</t>
+        </is>
+      </c>
+      <c r="M110" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5649,7 @@
           <t>總部-早午餐培訓儲備主管【需出差、具備餐飲管理經驗】桃園/需自備車輛</t>
         </is>
       </c>
-      <c r="H111" s="7" t="inlineStr">
+      <c r="H111" s="8" t="inlineStr">
         <is>
           <t>教育訓練人員</t>
         </is>
@@ -5410,6 +5662,11 @@
       <c r="J111" t="inlineStr">
         <is>
           <t>餐飲服務人員</t>
+        </is>
+      </c>
+      <c r="M111" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -5574,12 +5831,17 @@
           <t>【專案管理類】TQM儲備主管(外派泰國)</t>
         </is>
       </c>
-      <c r="H115" s="7" t="inlineStr">
+      <c r="H115" s="8" t="inlineStr">
         <is>
           <t>教育訓練人員</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
+        </is>
+      </c>
+      <c r="M115" s="9" t="inlineStr">
         <is>
           <t>儲備幹部</t>
         </is>
@@ -5617,7 +5879,7 @@
           <t>總部-早午餐培訓儲備主管【需出差、具備餐飲管理經驗】台南</t>
         </is>
       </c>
-      <c r="H116" s="7" t="inlineStr">
+      <c r="H116" s="8" t="inlineStr">
         <is>
           <t>教育訓練人員</t>
         </is>
@@ -5625,6 +5887,11 @@
       <c r="I116" t="inlineStr">
         <is>
           <t>餐飲主管</t>
+        </is>
+      </c>
+      <c r="M116" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6473,7 @@
           <t>教育訓練-儲備講師【訓練組】</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
+      <c r="H129" s="8" t="inlineStr">
         <is>
           <t>教育訓練人員</t>
         </is>
@@ -6219,6 +6486,11 @@
       <c r="J129" t="inlineStr">
         <is>
           <t>其他教育類老師</t>
+        </is>
+      </c>
+      <c r="M129" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6526,7 @@
           <t>【上市建材】教育訓練管理師/專員(海外業務管理部) 《享年終績效與季度分紅獎金》</t>
         </is>
       </c>
-      <c r="H130" s="7" t="inlineStr">
+      <c r="H130" s="8" t="inlineStr">
         <is>
           <t>教育訓練人員</t>
         </is>
@@ -6267,6 +6539,11 @@
       <c r="J130" s="7" t="inlineStr">
         <is>
           <t>國貿助理</t>
+        </is>
+      </c>
+      <c r="M130" s="9" t="inlineStr">
+        <is>
+          <t>國外業務人員</t>
         </is>
       </c>
     </row>
@@ -6398,7 +6675,7 @@
           <t>主管助理／秘書 (客服支援部)</t>
         </is>
       </c>
-      <c r="H133" s="7" t="inlineStr">
+      <c r="H133" s="8" t="inlineStr">
         <is>
           <t>人事助理</t>
         </is>
@@ -6421,6 +6698,11 @@
       <c r="L133" s="7" t="inlineStr">
         <is>
           <t>業務助理</t>
+        </is>
+      </c>
+      <c r="M133" s="9" t="inlineStr">
+        <is>
+          <t>客服人員</t>
         </is>
       </c>
     </row>
@@ -6542,7 +6824,7 @@
           <t>行政業務助理＜需精通英語＞</t>
         </is>
       </c>
-      <c r="H136" s="7" t="inlineStr">
+      <c r="H136" s="8" t="inlineStr">
         <is>
           <t>人事助理</t>
         </is>
@@ -6550,6 +6832,11 @@
       <c r="I136" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M136" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6915,7 @@
           <t>會計助理</t>
         </is>
       </c>
-      <c r="H138" s="7" t="inlineStr">
+      <c r="H138" s="8" t="inlineStr">
         <is>
           <t>人事助理</t>
         </is>
@@ -6636,6 +6923,11 @@
       <c r="I138" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M138" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -6762,7 +7054,7 @@
           <t>聖約翰科技大學【徵聘儲備人員】徵聘約計畫及約聘行政人員數名</t>
         </is>
       </c>
-      <c r="H141" s="7" t="inlineStr">
+      <c r="H141" s="8" t="inlineStr">
         <is>
           <t>人事助理</t>
         </is>
@@ -6775,6 +7067,11 @@
       <c r="J141" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M141" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -6858,7 +7155,7 @@
           <t>[日商]台灣善商-業務助理</t>
         </is>
       </c>
-      <c r="H143" s="7" t="inlineStr">
+      <c r="H143" s="8" t="inlineStr">
         <is>
           <t>人事助理</t>
         </is>
@@ -6871,6 +7168,11 @@
       <c r="J143" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M143" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7304,7 @@
           <t>【人資儲備主管】招募 × 制度 × 數據｜培養未來人資管理者</t>
         </is>
       </c>
-      <c r="H146" s="7" t="inlineStr">
+      <c r="H146" s="8" t="inlineStr">
         <is>
           <t>人事助理</t>
         </is>
@@ -7015,6 +7317,11 @@
       <c r="J146" s="7" t="inlineStr">
         <is>
           <t>教育訓練人員</t>
+        </is>
+      </c>
+      <c r="M146" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -7050,7 +7357,7 @@
           <t>人資總務助理</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
+      <c r="H147" s="8" t="inlineStr">
         <is>
           <t>人事助理</t>
         </is>
@@ -7061,6 +7368,11 @@
         </is>
       </c>
       <c r="J147" s="7" t="inlineStr">
+        <is>
+          <t>總務人員</t>
+        </is>
+      </c>
+      <c r="M147" s="9" t="inlineStr">
         <is>
           <t>總務人員</t>
         </is>
@@ -7098,7 +7410,7 @@
           <t>業務助理</t>
         </is>
       </c>
-      <c r="H148" s="7" t="inlineStr">
+      <c r="H148" s="8" t="inlineStr">
         <is>
           <t>人事助理</t>
         </is>
@@ -7111,6 +7423,11 @@
       <c r="J148" t="inlineStr">
         <is>
           <t>檔案資料管理人員</t>
+        </is>
+      </c>
+      <c r="M148" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -7318,9 +7635,14 @@
           <t>【2026鴻海集團-AI雲端實習生】CESBG專區-人資實習生-教育訓練</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
+      <c r="H153" s="8" t="inlineStr">
         <is>
           <t>人事助理</t>
+        </is>
+      </c>
+      <c r="M153" s="9" t="inlineStr">
+        <is>
+          <t>教育訓練人員</t>
         </is>
       </c>
     </row>
@@ -7698,12 +8020,17 @@
           <t>人資總務部 助理</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
+      <c r="H163" s="8" t="inlineStr">
         <is>
           <t>人事助理</t>
         </is>
       </c>
       <c r="I163" s="7" t="inlineStr">
+        <is>
+          <t>總務人員</t>
+        </is>
+      </c>
+      <c r="M163" s="9" t="inlineStr">
         <is>
           <t>總務人員</t>
         </is>
@@ -7789,7 +8116,7 @@
           <t>人資_招募訓練業務助理</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
+      <c r="H165" s="8" t="inlineStr">
         <is>
           <t>人事助理</t>
         </is>
@@ -7802,6 +8129,11 @@
       <c r="J165" t="inlineStr">
         <is>
           <t>人事／人力資源專員</t>
+        </is>
+      </c>
+      <c r="M165" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -7981,7 +8313,7 @@
           <t>出納，協助主管交待事務交辦出貨</t>
         </is>
       </c>
-      <c r="H169" s="7" t="inlineStr">
+      <c r="H169" s="8" t="inlineStr">
         <is>
           <t>人事助理</t>
         </is>
@@ -7992,6 +8324,11 @@
         </is>
       </c>
       <c r="J169" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
+        </is>
+      </c>
+      <c r="M169" s="9" t="inlineStr">
         <is>
           <t>會計／出納／記帳人員</t>
         </is>
@@ -8504,7 +8841,7 @@
           <t>●業務助理(嘉義檜意村加盟店)</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
+      <c r="H180" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -8512,6 +8849,11 @@
       <c r="I180" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M180" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -8547,7 +8889,7 @@
           <t>行政業務助理</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
+      <c r="H181" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -8560,6 +8902,11 @@
       <c r="J181" s="7" t="inlineStr">
         <is>
           <t>總務人員</t>
+        </is>
+      </c>
+      <c r="M181" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -8823,9 +9170,14 @@
           <t>健檢課-業務專員</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
+      <c r="H188" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M188" s="9" t="inlineStr">
+        <is>
+          <t>國內業務人員</t>
         </is>
       </c>
     </row>
@@ -8975,7 +9327,7 @@
           <t>行政客服專員-護理之家(鼓山區)</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
+      <c r="H192" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -8983,6 +9335,11 @@
       <c r="I192" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M192" s="9" t="inlineStr">
+        <is>
+          <t>客服人員</t>
         </is>
       </c>
     </row>
@@ -9104,7 +9461,7 @@
           <t>業務助理(嘉義檜意村加盟店)</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
+      <c r="H195" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -9112,6 +9469,11 @@
       <c r="I195" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M195" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -9147,7 +9509,7 @@
           <t>徵業務助理(嘉義檜意村加盟店)</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
+      <c r="H196" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -9155,6 +9517,11 @@
       <c r="I196" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M196" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -9190,7 +9557,7 @@
           <t>【工研院產科國際所】業務暨客服助理派遣人員(0Q400)_台北、新竹皆可 TCL1(L)</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
+      <c r="H197" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -9203,6 +9570,11 @@
       <c r="J197" s="7" t="inlineStr">
         <is>
           <t>其他專案管理師</t>
+        </is>
+      </c>
+      <c r="M197" s="9" t="inlineStr">
+        <is>
+          <t>客服人員</t>
         </is>
       </c>
     </row>
@@ -9362,7 +9734,7 @@
           <t>業務行政助理</t>
         </is>
       </c>
-      <c r="H201" s="7" t="inlineStr">
+      <c r="H201" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -9370,6 +9742,11 @@
       <c r="I201" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M201" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -9405,7 +9782,7 @@
           <t>行政助理/業務助理(內勤工作)</t>
         </is>
       </c>
-      <c r="H202" s="7" t="inlineStr">
+      <c r="H202" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -9413,6 +9790,11 @@
       <c r="I202" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M202" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -9496,7 +9878,7 @@
           <t>正職業務助理(月領45000元**開發獎金另計**AM:8:00~PM:17:00)(請電洽宋先生 0915090281)</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
+      <c r="H204" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -9509,6 +9891,11 @@
       <c r="J204" t="inlineStr">
         <is>
           <t>總機／接待／櫃檯人員</t>
+        </is>
+      </c>
+      <c r="M204" s="9" t="inlineStr">
+        <is>
+          <t>產品經理</t>
         </is>
       </c>
     </row>
@@ -9544,7 +9931,7 @@
           <t>行政儲備幹部</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
+      <c r="H205" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -9557,6 +9944,11 @@
       <c r="J205" s="7" t="inlineStr">
         <is>
           <t>補習班導師</t>
+        </is>
+      </c>
+      <c r="M205" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -9635,7 +10027,7 @@
           <t>✦總務人員-行政(總務部業務員)</t>
         </is>
       </c>
-      <c r="H207" s="7" t="inlineStr">
+      <c r="H207" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -9646,6 +10038,11 @@
         </is>
       </c>
       <c r="J207" t="inlineStr">
+        <is>
+          <t>總務人員</t>
+        </is>
+      </c>
+      <c r="M207" s="9" t="inlineStr">
         <is>
           <t>總務人員</t>
         </is>
@@ -9683,7 +10080,7 @@
           <t>北區倉儲部-行政組 儲備幹部</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
+      <c r="H208" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -9696,6 +10093,11 @@
       <c r="J208" s="7" t="inlineStr">
         <is>
           <t>檔案資料管理人員</t>
+        </is>
+      </c>
+      <c r="M208" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -9817,9 +10219,14 @@
           <t>會計行政助理</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
+      <c r="H211" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M211" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -9855,7 +10262,7 @@
           <t>美夢成真國際美容機構【福和店】店務行政會計</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr">
+      <c r="H212" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -9863,6 +10270,11 @@
       <c r="I212" s="7" t="inlineStr">
         <is>
           <t>檔案資料管理人員</t>
+        </is>
+      </c>
+      <c r="M212" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -9941,7 +10353,7 @@
           <t>【永安店】店務行政會計</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
+      <c r="H214" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -9949,6 +10361,11 @@
       <c r="I214" s="7" t="inlineStr">
         <is>
           <t>檔案資料管理人員</t>
+        </is>
+      </c>
+      <c r="M214" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -10060,9 +10477,14 @@
           <t>◆學生可◆【業務助理】純內勤工作 #近捷運站｜歡迎進修部同學或轉職GAP BIS_211</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
+      <c r="H217" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M217" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -10136,9 +10558,14 @@
           <t>行政儲備幹部（機料部）</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
+      <c r="H219" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M219" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -10174,9 +10601,14 @@
           <t>經營管理組-行政助理管理師(儲備主管)</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
+      <c r="H220" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M220" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -10212,9 +10644,14 @@
           <t>行政業務助理(型鋼)</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
+      <c r="H221" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M221" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -10250,9 +10687,14 @@
           <t>大林分院-影像醫學科-辦事員(儲備)</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
+      <c r="H222" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M222" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -10412,7 +10854,7 @@
           <t>#非業務 純書審免面試【市區行政內勤】知名人壽內勤行政業務助理｜工作單純穩定、薪資32k起｜配合加班 #純行政內勤（KTS_1298）</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
+      <c r="H226" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -10425,6 +10867,11 @@
       <c r="J226" t="inlineStr">
         <is>
           <t>電腦操作／資料輸入</t>
+        </is>
+      </c>
+      <c r="M226" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -10460,7 +10907,7 @@
           <t>【零售】電信業務行政助理</t>
         </is>
       </c>
-      <c r="H227" s="7" t="inlineStr">
+      <c r="H227" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -10473,6 +10920,11 @@
       <c r="J227" t="inlineStr">
         <is>
           <t>電腦操作／資料輸入</t>
+        </is>
+      </c>
+      <c r="M227" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -10508,7 +10960,7 @@
           <t>業務助理(林口區)</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
+      <c r="H228" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -10521,6 +10973,11 @@
       <c r="J228" t="inlineStr">
         <is>
           <t>電腦操作／資料輸入</t>
+        </is>
+      </c>
+      <c r="M228" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -10642,7 +11099,7 @@
           <t>★韓國電商龍頭★【酷澎Coupang】電商業務助理 Associate, Catalog Operation_OCS330</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr">
+      <c r="H231" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -10650,6 +11107,11 @@
       <c r="I231" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M231" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -10905,7 +11367,7 @@
           <t>行政助理(儲備幹部)</t>
         </is>
       </c>
-      <c r="H237" s="7" t="inlineStr">
+      <c r="H237" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -10918,6 +11380,11 @@
       <c r="J237" t="inlineStr">
         <is>
           <t>電腦操作／資料輸入</t>
+        </is>
+      </c>
+      <c r="M237" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -10953,7 +11420,7 @@
           <t>【外商】生管業務助理（契約）</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr">
+      <c r="H238" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -10961,6 +11428,11 @@
       <c r="I238" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M238" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -10996,7 +11468,7 @@
           <t>會計</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr">
+      <c r="H239" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -11004,6 +11476,11 @@
       <c r="I239" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M239" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -11039,7 +11516,7 @@
           <t>業務助理</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr">
+      <c r="H240" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -11052,6 +11529,11 @@
       <c r="J240" s="7" t="inlineStr">
         <is>
           <t>總務人員</t>
+        </is>
+      </c>
+      <c r="M240" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11569,7 @@
           <t>業務行政助理專員(瑞芳)</t>
         </is>
       </c>
-      <c r="H241" s="7" t="inlineStr">
+      <c r="H241" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -11095,6 +11577,11 @@
       <c r="I241" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M241" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -11173,7 +11660,7 @@
           <t>會計文書助理</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr">
+      <c r="H243" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -11186,6 +11673,11 @@
       <c r="J243" s="7" t="inlineStr">
         <is>
           <t>總務人員</t>
+        </is>
+      </c>
+      <c r="M243" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -11221,7 +11713,7 @@
           <t>業務助理/專員(捷絲旅)</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr">
+      <c r="H244" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -11234,6 +11726,11 @@
       <c r="J244" s="7" t="inlineStr">
         <is>
           <t>秘書</t>
+        </is>
+      </c>
+      <c r="M244" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11766,7 @@
           <t>●儲備店務秘書●行政文書</t>
         </is>
       </c>
-      <c r="H245" s="7" t="inlineStr">
+      <c r="H245" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -11282,6 +11779,11 @@
       <c r="J245" t="inlineStr">
         <is>
           <t>秘書</t>
+        </is>
+      </c>
+      <c r="M245" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -11413,7 +11915,7 @@
           <t>行政儲備幹部</t>
         </is>
       </c>
-      <c r="H248" t="inlineStr">
+      <c r="H248" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -11421,6 +11923,11 @@
       <c r="I248" t="inlineStr">
         <is>
           <t>特別助理</t>
+        </is>
+      </c>
+      <c r="M248" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -11456,9 +11963,14 @@
           <t>行政會計人員</t>
         </is>
       </c>
-      <c r="H249" t="inlineStr">
+      <c r="H249" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M249" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -11722,9 +12234,14 @@
           <t>業務助理</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr">
+      <c r="H256" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M256" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -11798,9 +12315,14 @@
           <t>115年度行政及業務輔助人力勞務委外採購案（士林）</t>
         </is>
       </c>
-      <c r="H258" s="7" t="inlineStr">
+      <c r="H258" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M258" s="9" t="inlineStr">
+        <is>
+          <t>採購人員</t>
         </is>
       </c>
     </row>
@@ -11836,7 +12358,7 @@
           <t>【外貿協會】專案經理(創新業務中心/產業創新組)</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr">
+      <c r="H259" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -11849,6 +12371,11 @@
       <c r="J259" t="inlineStr">
         <is>
           <t>其他專案管理師</t>
+        </is>
+      </c>
+      <c r="M259" s="9" t="inlineStr">
+        <is>
+          <t>專案經理</t>
         </is>
       </c>
     </row>
@@ -11960,9 +12487,14 @@
           <t>門市行政儲備主管</t>
         </is>
       </c>
-      <c r="H262" t="inlineStr">
+      <c r="H262" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M262" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -12046,7 +12578,7 @@
           <t>【短期約聘】中秋活動業務助理/電話行銷人員</t>
         </is>
       </c>
-      <c r="H264" t="inlineStr">
+      <c r="H264" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -12059,6 +12591,11 @@
       <c r="J264" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M264" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -12137,7 +12674,7 @@
           <t>老鷹地產中信房屋會計</t>
         </is>
       </c>
-      <c r="H266" t="inlineStr">
+      <c r="H266" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -12145,6 +12682,11 @@
       <c r="I266" s="7" t="inlineStr">
         <is>
           <t>秘書</t>
+        </is>
+      </c>
+      <c r="M266" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -12223,7 +12765,7 @@
           <t>台南區-人資部-薪酬會計</t>
         </is>
       </c>
-      <c r="H268" t="inlineStr">
+      <c r="H268" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -12236,6 +12778,11 @@
       <c r="J268" s="7" t="inlineStr">
         <is>
           <t>人事／人力資源專員</t>
+        </is>
+      </c>
+      <c r="M268" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -12511,12 +13058,17 @@
           <t>鍋癮有限公司 總管理處 會計/行政/人資人員</t>
         </is>
       </c>
-      <c r="H274" t="inlineStr">
+      <c r="H274" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
+        </is>
+      </c>
+      <c r="M274" s="9" t="inlineStr">
         <is>
           <t>會計／出納／記帳人員</t>
         </is>
@@ -12597,7 +13149,7 @@
           <t>《網拍電商》電商業務助理 客服小編 行政助理</t>
         </is>
       </c>
-      <c r="H276" s="7" t="inlineStr">
+      <c r="H276" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -12610,6 +13162,11 @@
       <c r="J276" s="7" t="inlineStr">
         <is>
           <t>美編人員</t>
+        </is>
+      </c>
+      <c r="M276" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -12645,7 +13202,7 @@
           <t>人資會計</t>
         </is>
       </c>
-      <c r="H277" t="inlineStr">
+      <c r="H277" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -12658,6 +13215,11 @@
       <c r="J277" s="7" t="inlineStr">
         <is>
           <t>總務人員</t>
+        </is>
+      </c>
+      <c r="M277" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -12693,7 +13255,7 @@
           <t>人資會計專員</t>
         </is>
       </c>
-      <c r="H278" t="inlineStr">
+      <c r="H278" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -12701,6 +13263,11 @@
       <c r="I278" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M278" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -12736,7 +13303,7 @@
           <t>行政儲備幹部(宜蘭廠)</t>
         </is>
       </c>
-      <c r="H279" t="inlineStr">
+      <c r="H279" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -12744,6 +13311,11 @@
       <c r="I279" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M279" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -12779,7 +13351,7 @@
           <t>業務助理</t>
         </is>
       </c>
-      <c r="H280" t="inlineStr">
+      <c r="H280" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -12787,6 +13359,11 @@
       <c r="I280" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M280" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13710,7 @@
           <t>辦公室業務助理</t>
         </is>
       </c>
-      <c r="H288" t="inlineStr">
+      <c r="H288" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -13146,6 +13723,11 @@
       <c r="J288" t="inlineStr">
         <is>
           <t>總機／接待／櫃檯人員</t>
+        </is>
+      </c>
+      <c r="M288" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -13421,7 +14003,7 @@
           <t>★韓國電商龍頭★【酷澎Coupang】行政業務助理 Associate, Catalog Operation _OCS330</t>
         </is>
       </c>
-      <c r="H294" t="inlineStr">
+      <c r="H294" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -13434,6 +14016,11 @@
       <c r="J294" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M294" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -13517,7 +14104,7 @@
           <t>房仲店頭-業務助理</t>
         </is>
       </c>
-      <c r="H296" t="inlineStr">
+      <c r="H296" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -13530,6 +14117,11 @@
       <c r="J296" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M296" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -13565,7 +14157,7 @@
           <t>不動產業務助理(住商土城日月光捷運店)</t>
         </is>
       </c>
-      <c r="H297" t="inlineStr">
+      <c r="H297" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -13578,6 +14170,11 @@
       <c r="J297" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M297" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -13613,7 +14210,7 @@
           <t>【社宅業務助理】-總公司-資產管理處</t>
         </is>
       </c>
-      <c r="H298" t="inlineStr">
+      <c r="H298" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -13626,6 +14223,11 @@
       <c r="J298" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M298" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -13661,9 +14263,14 @@
           <t>甲種、丙種業務主管 / 排班管理</t>
         </is>
       </c>
-      <c r="H299" t="inlineStr">
+      <c r="H299" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M299" s="9" t="inlineStr">
+        <is>
+          <t>國內業務主管</t>
         </is>
       </c>
     </row>
@@ -13780,9 +14387,14 @@
           <t>行政會計</t>
         </is>
       </c>
-      <c r="H302" t="inlineStr">
+      <c r="H302" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M302" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -14137,7 +14749,7 @@
           <t>行政儲備幹部(台南市永康區)</t>
         </is>
       </c>
-      <c r="H311" t="inlineStr">
+      <c r="H311" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -14145,6 +14757,11 @@
       <c r="I311" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M311" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -14180,7 +14797,7 @@
           <t>工研院產科國際所_業務暨客服助理派遣人員(0Q200)_台北、新竹皆可</t>
         </is>
       </c>
-      <c r="H312" t="inlineStr">
+      <c r="H312" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -14188,6 +14805,11 @@
       <c r="I312" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M312" s="9" t="inlineStr">
+        <is>
+          <t>客服人員</t>
         </is>
       </c>
     </row>
@@ -14352,7 +14974,7 @@
           <t>【優利國際】派駐食藥署秘書室文書及檔案業務人員</t>
         </is>
       </c>
-      <c r="H316" t="inlineStr">
+      <c r="H316" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -14360,6 +14982,11 @@
       <c r="I316" s="7" t="inlineStr">
         <is>
           <t>公家機關相關人員</t>
+        </is>
+      </c>
+      <c r="M316" s="9" t="inlineStr">
+        <is>
+          <t>國內業務人員</t>
         </is>
       </c>
     </row>
@@ -14443,7 +15070,7 @@
           <t>事務員(健檢課)-具備會計背景</t>
         </is>
       </c>
-      <c r="H318" t="inlineStr">
+      <c r="H318" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -14451,6 +15078,11 @@
       <c r="I318" s="7" t="inlineStr">
         <is>
           <t>醫院行政管理人員</t>
+        </is>
+      </c>
+      <c r="M318" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -14572,7 +15204,7 @@
           <t>現場管理儲備幹部(土城)</t>
         </is>
       </c>
-      <c r="H321" t="inlineStr">
+      <c r="H321" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -14585,6 +15217,11 @@
       <c r="J321" s="7" t="inlineStr">
         <is>
           <t>客服人員</t>
+        </is>
+      </c>
+      <c r="M321" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -14620,7 +15257,7 @@
           <t>現場管理儲備幹部(中和)</t>
         </is>
       </c>
-      <c r="H322" t="inlineStr">
+      <c r="H322" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -14633,6 +15270,11 @@
       <c r="J322" s="7" t="inlineStr">
         <is>
           <t>客服人員</t>
+        </is>
+      </c>
+      <c r="M322" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -14668,7 +15310,7 @@
           <t>現場管理儲備幹部(永康)_大夜班</t>
         </is>
       </c>
-      <c r="H323" t="inlineStr">
+      <c r="H323" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -14681,6 +15323,11 @@
       <c r="J323" s="7" t="inlineStr">
         <is>
           <t>客服人員</t>
+        </is>
+      </c>
+      <c r="M323" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -14716,7 +15363,7 @@
           <t>♕ 住商竹南大埔店-業務助理</t>
         </is>
       </c>
-      <c r="H324" t="inlineStr">
+      <c r="H324" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -14729,6 +15376,11 @@
       <c r="J324" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M324" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -15040,7 +15692,7 @@
           <t>行政會計(嘉義大埔美)</t>
         </is>
       </c>
-      <c r="H332" t="inlineStr">
+      <c r="H332" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -15053,6 +15705,11 @@
       <c r="J332" t="inlineStr">
         <is>
           <t>電腦操作／資料輸入</t>
+        </is>
+      </c>
+      <c r="M332" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -15136,7 +15793,7 @@
           <t>【零售】電信業務行政助理(職務代理人)</t>
         </is>
       </c>
-      <c r="H334" s="7" t="inlineStr">
+      <c r="H334" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -15149,6 +15806,11 @@
       <c r="J334" t="inlineStr">
         <is>
           <t>電腦操作／資料輸入</t>
+        </is>
+      </c>
+      <c r="M334" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -15227,7 +15889,7 @@
           <t>業務行政助理專員(高雄)</t>
         </is>
       </c>
-      <c r="H336" t="inlineStr">
+      <c r="H336" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -15235,6 +15897,11 @@
       <c r="I336" t="inlineStr">
         <is>
           <t>電腦操作／資料輸入</t>
+        </is>
+      </c>
+      <c r="M336" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -15404,7 +16071,7 @@
           <t>誠徵 全方位 業務助理 願意學習者優先</t>
         </is>
       </c>
-      <c r="H340" t="inlineStr">
+      <c r="H340" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -15412,6 +16079,11 @@
       <c r="I340" t="inlineStr">
         <is>
           <t>電腦操作／資料輸入</t>
+        </is>
+      </c>
+      <c r="M340" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -15710,9 +16382,14 @@
           <t>115年度行政及業務輔助人力勞務委外採購案（內湖）</t>
         </is>
       </c>
-      <c r="H347" s="7" t="inlineStr">
+      <c r="H347" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M347" s="9" t="inlineStr">
+        <is>
+          <t>採購人員</t>
         </is>
       </c>
     </row>
@@ -15786,9 +16463,14 @@
           <t>建設/業務部客服(高雄)</t>
         </is>
       </c>
-      <c r="H349" t="inlineStr">
+      <c r="H349" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M349" s="9" t="inlineStr">
+        <is>
+          <t>客服人員</t>
         </is>
       </c>
     </row>
@@ -16067,7 +16749,7 @@
           <t>行政儲備師資</t>
         </is>
       </c>
-      <c r="H356" s="7" t="inlineStr">
+      <c r="H356" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -16080,6 +16762,11 @@
       <c r="J356" s="7" t="inlineStr">
         <is>
           <t>美編人員</t>
+        </is>
+      </c>
+      <c r="M356" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -16378,12 +17065,17 @@
           <t>DAYOU 大祐珠寶招募門市業務助理</t>
         </is>
       </c>
-      <c r="H363" t="inlineStr">
+      <c r="H363" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
+        <is>
+          <t>業務助理</t>
+        </is>
+      </c>
+      <c r="M363" s="9" t="inlineStr">
         <is>
           <t>業務助理</t>
         </is>
@@ -16421,7 +17113,7 @@
           <t>採購部儲備主管(台中西屯總公司)</t>
         </is>
       </c>
-      <c r="H364" t="inlineStr">
+      <c r="H364" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -16429,6 +17121,11 @@
       <c r="I364" s="7" t="inlineStr">
         <is>
           <t>採購人員</t>
+        </is>
+      </c>
+      <c r="M364" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -16464,12 +17161,17 @@
           <t>業務部行政儲備主管(台北/台南/高雄)_知名建設公司 (3009629)</t>
         </is>
       </c>
-      <c r="H365" t="inlineStr">
+      <c r="H365" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
+        </is>
+      </c>
+      <c r="M365" s="9" t="inlineStr">
         <is>
           <t>儲備幹部</t>
         </is>
@@ -16550,12 +17252,17 @@
           <t>醫事課-助理管理師(儲備主管)</t>
         </is>
       </c>
-      <c r="H367" t="inlineStr">
+      <c r="H367" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
+        </is>
+      </c>
+      <c r="M367" s="9" t="inlineStr">
         <is>
           <t>儲備幹部</t>
         </is>
@@ -16803,12 +17510,17 @@
           <t>業務會計人員</t>
         </is>
       </c>
-      <c r="H373" t="inlineStr">
+      <c r="H373" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
+        </is>
+      </c>
+      <c r="M373" s="9" t="inlineStr">
         <is>
           <t>會計／出納／記帳人員</t>
         </is>
@@ -17205,7 +17917,7 @@
           <t>業務行政助理專員(大肚)</t>
         </is>
       </c>
-      <c r="H382" s="7" t="inlineStr">
+      <c r="H382" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -17218,6 +17930,11 @@
       <c r="J382" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M382" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -17349,7 +18066,7 @@
           <t>大型電商行政團隊擴編#朝九晚六#交通便利#未來發展性佳#行政/人事/會計/設計皆招募中！</t>
         </is>
       </c>
-      <c r="H385" t="inlineStr">
+      <c r="H385" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -17362,6 +18079,11 @@
       <c r="J385" s="7" t="inlineStr">
         <is>
           <t>人事助理</t>
+        </is>
+      </c>
+      <c r="M385" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -17397,7 +18119,7 @@
           <t>儲備幹部/業務助理-新北中和總公司</t>
         </is>
       </c>
-      <c r="H386" t="inlineStr">
+      <c r="H386" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -17410,6 +18132,11 @@
       <c r="J386" t="inlineStr">
         <is>
           <t>基層管理幹部</t>
+        </is>
+      </c>
+      <c r="M386" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -17445,7 +18172,7 @@
           <t>儲備幹部，業務主管，行銷業務</t>
         </is>
       </c>
-      <c r="H387" t="inlineStr">
+      <c r="H387" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -17458,6 +18185,11 @@
       <c r="J387" t="inlineStr">
         <is>
           <t>基層管理幹部</t>
+        </is>
+      </c>
+      <c r="M387" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -17541,7 +18273,7 @@
           <t>業務主管助理</t>
         </is>
       </c>
-      <c r="H389" t="inlineStr">
+      <c r="H389" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -17554,6 +18286,11 @@
       <c r="J389" t="inlineStr">
         <is>
           <t>特別助理</t>
+        </is>
+      </c>
+      <c r="M389" s="9" t="inlineStr">
+        <is>
+          <t>國內業務主管</t>
         </is>
       </c>
     </row>
@@ -17589,7 +18326,7 @@
           <t>高雄【財務會計專員】苓雅區</t>
         </is>
       </c>
-      <c r="H390" t="inlineStr">
+      <c r="H390" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -17602,6 +18339,11 @@
       <c r="J390" t="inlineStr">
         <is>
           <t>總機／接待／櫃檯人員</t>
+        </is>
+      </c>
+      <c r="M390" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -17733,7 +18475,7 @@
           <t>倉管儲備人員</t>
         </is>
       </c>
-      <c r="H393" t="inlineStr">
+      <c r="H393" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -17746,6 +18488,11 @@
       <c r="J393" s="7" t="inlineStr">
         <is>
           <t>理貨人員</t>
+        </is>
+      </c>
+      <c r="M393" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -17781,7 +18528,7 @@
           <t>高雄岡山｜低溫物流業務助理</t>
         </is>
       </c>
-      <c r="H394" t="inlineStr">
+      <c r="H394" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -17794,6 +18541,11 @@
       <c r="J394" s="7" t="inlineStr">
         <is>
           <t>廠務助理</t>
+        </is>
+      </c>
+      <c r="M394" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -17829,7 +18581,7 @@
           <t>🇯🇵天母日文補習班🇯🇵儲備幹部</t>
         </is>
       </c>
-      <c r="H395" t="inlineStr">
+      <c r="H395" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -17842,6 +18594,11 @@
       <c r="J395" t="inlineStr">
         <is>
           <t>補習班主任／主管</t>
+        </is>
+      </c>
+      <c r="M395" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -17973,7 +18730,7 @@
           <t>儲備人員(身心障礙、工作地點:台北中山區)</t>
         </is>
       </c>
-      <c r="H398" t="inlineStr">
+      <c r="H398" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -17986,6 +18743,11 @@
       <c r="J398" s="7" t="inlineStr">
         <is>
           <t>資訊助理人員</t>
+        </is>
+      </c>
+      <c r="M398" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -18155,7 +18917,7 @@
           <t>TOYOTA顧客服務專員-市政廠(儲備幹部)-非汽車銷售業務員(TCL1)</t>
         </is>
       </c>
-      <c r="H402" t="inlineStr">
+      <c r="H402" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -18168,6 +18930,11 @@
       <c r="J402" s="7" t="inlineStr">
         <is>
           <t>門市／店員／專櫃人員</t>
+        </is>
+      </c>
+      <c r="M402" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -18251,7 +19018,7 @@
           <t>管理部-業務助理</t>
         </is>
       </c>
-      <c r="H404" t="inlineStr">
+      <c r="H404" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -18264,6 +19031,11 @@
       <c r="J404" s="7" t="inlineStr">
         <is>
           <t>檔案資料管理人員</t>
+        </is>
+      </c>
+      <c r="M404" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -18299,7 +19071,7 @@
           <t>OP／旅行社人員、業務助理、內勤業務</t>
         </is>
       </c>
-      <c r="H405" t="inlineStr">
+      <c r="H405" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -18312,6 +19084,11 @@
       <c r="J405" s="7" t="inlineStr">
         <is>
           <t>檔案資料管理人員</t>
+        </is>
+      </c>
+      <c r="M405" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -18347,7 +19124,7 @@
           <t>行政業務助理</t>
         </is>
       </c>
-      <c r="H406" t="inlineStr">
+      <c r="H406" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -18355,6 +19132,11 @@
       <c r="I406" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M406" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -18390,7 +19172,7 @@
           <t>物流業務主管</t>
         </is>
       </c>
-      <c r="H407" t="inlineStr">
+      <c r="H407" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -18403,6 +19185,11 @@
       <c r="J407" t="inlineStr">
         <is>
           <t>儲備幹部</t>
+        </is>
+      </c>
+      <c r="M407" s="9" t="inlineStr">
+        <is>
+          <t>國內業務主管</t>
         </is>
       </c>
     </row>
@@ -18534,7 +19321,7 @@
           <t>TOYOTA汽車-顧客服務專員-員林廠-非汽車銷售業務員(TCL1)</t>
         </is>
       </c>
-      <c r="H410" t="inlineStr">
+      <c r="H410" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -18545,6 +19332,11 @@
         </is>
       </c>
       <c r="J410" s="7" t="inlineStr">
+        <is>
+          <t>客服人員</t>
+        </is>
+      </c>
+      <c r="M410" s="9" t="inlineStr">
         <is>
           <t>客服人員</t>
         </is>
@@ -18630,7 +19422,7 @@
           <t>售後服務業務專員</t>
         </is>
       </c>
-      <c r="H412" t="inlineStr">
+      <c r="H412" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -18643,6 +19435,11 @@
       <c r="J412" s="7" t="inlineStr">
         <is>
           <t>機械工程師</t>
+        </is>
+      </c>
+      <c r="M412" s="9" t="inlineStr">
+        <is>
+          <t>國內業務人員</t>
         </is>
       </c>
     </row>
@@ -18726,7 +19523,7 @@
           <t>商品部儲備主管</t>
         </is>
       </c>
-      <c r="H414" t="inlineStr">
+      <c r="H414" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -18739,6 +19536,11 @@
       <c r="J414" s="7" t="inlineStr">
         <is>
           <t>採購主管</t>
+        </is>
+      </c>
+      <c r="M414" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -18774,7 +19576,7 @@
           <t>儲備教保員</t>
         </is>
       </c>
-      <c r="H415" s="7" t="inlineStr">
+      <c r="H415" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -18787,6 +19589,11 @@
       <c r="J415" t="inlineStr">
         <is>
           <t>幼教老師</t>
+        </is>
+      </c>
+      <c r="M415" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -18822,7 +19629,7 @@
           <t>行政會計助理人員</t>
         </is>
       </c>
-      <c r="H416" t="inlineStr">
+      <c r="H416" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -18835,6 +19642,11 @@
       <c r="J416" s="7" t="inlineStr">
         <is>
           <t>業務助理</t>
+        </is>
+      </c>
+      <c r="M416" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -19004,7 +19816,7 @@
           <t>會計</t>
         </is>
       </c>
-      <c r="H420" t="inlineStr">
+      <c r="H420" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -19012,6 +19824,11 @@
       <c r="I420" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M420" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -19095,7 +19912,7 @@
           <t>行政會計人員、行政助理</t>
         </is>
       </c>
-      <c r="H422" s="7" t="inlineStr">
+      <c r="H422" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -19108,6 +19925,11 @@
       <c r="J422" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M422" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -19191,7 +20013,7 @@
           <t>派遣外商【行政儲備幹部】36-40K｜具晉升加薪&amp;轉正機會 _106AH</t>
         </is>
       </c>
-      <c r="H424" t="inlineStr">
+      <c r="H424" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -19204,6 +20026,11 @@
       <c r="J424" s="7" t="inlineStr">
         <is>
           <t>資料庫管理人員</t>
+        </is>
+      </c>
+      <c r="M424" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -19287,7 +20114,7 @@
           <t>工務/業務助理</t>
         </is>
       </c>
-      <c r="H426" t="inlineStr">
+      <c r="H426" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -19300,6 +20127,11 @@
       <c r="J426" s="7" t="inlineStr">
         <is>
           <t>總務人員</t>
+        </is>
+      </c>
+      <c r="M426" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -19335,7 +20167,7 @@
           <t>行政助理(儲備總務)</t>
         </is>
       </c>
-      <c r="H427" s="7" t="inlineStr">
+      <c r="H427" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -19348,6 +20180,11 @@
       <c r="J427" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M427" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -19767,7 +20604,7 @@
           <t>雙橡園開發_客戶關係部業務專員</t>
         </is>
       </c>
-      <c r="H436" t="inlineStr">
+      <c r="H436" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -19780,6 +20617,11 @@
       <c r="J436" s="7" t="inlineStr">
         <is>
           <t>秘書</t>
+        </is>
+      </c>
+      <c r="M436" s="9" t="inlineStr">
+        <is>
+          <t>國內業務人員</t>
         </is>
       </c>
     </row>
@@ -19815,7 +20657,7 @@
           <t>居家長照 行政人資會計</t>
         </is>
       </c>
-      <c r="H437" t="inlineStr">
+      <c r="H437" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -19826,6 +20668,11 @@
         </is>
       </c>
       <c r="J437" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
+        </is>
+      </c>
+      <c r="M437" s="9" t="inlineStr">
         <is>
           <t>會計／出納／記帳人員</t>
         </is>
@@ -19863,7 +20710,7 @@
           <t>廠務管理儲備幹部</t>
         </is>
       </c>
-      <c r="H438" t="inlineStr">
+      <c r="H438" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -19876,6 +20723,11 @@
       <c r="J438" t="inlineStr">
         <is>
           <t>領班／管理幹部</t>
+        </is>
+      </c>
+      <c r="M438" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -19911,7 +20763,7 @@
           <t>TOYOTA顧客服務專員-東海廠(儲備幹部)-非汽車銷售業務員(TCL1)</t>
         </is>
       </c>
-      <c r="H439" t="inlineStr">
+      <c r="H439" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -19924,6 +20776,11 @@
       <c r="J439" t="inlineStr">
         <is>
           <t>總機／接待／櫃檯人員</t>
+        </is>
+      </c>
+      <c r="M439" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -20007,7 +20864,7 @@
           <t>門市行政/客服人員</t>
         </is>
       </c>
-      <c r="H441" s="7" t="inlineStr">
+      <c r="H441" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -20020,6 +20877,11 @@
       <c r="J441" s="7" t="inlineStr">
         <is>
           <t>總機／接待／櫃檯人員</t>
+        </is>
+      </c>
+      <c r="M441" s="9" t="inlineStr">
+        <is>
+          <t>客服人員</t>
         </is>
       </c>
     </row>
@@ -20055,7 +20917,7 @@
           <t>監理所業務人員(台北信義區)</t>
         </is>
       </c>
-      <c r="H442" t="inlineStr">
+      <c r="H442" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -20068,6 +20930,11 @@
       <c r="J442" s="7" t="inlineStr">
         <is>
           <t>小客車／小貨車司機</t>
+        </is>
+      </c>
+      <c r="M442" s="9" t="inlineStr">
+        <is>
+          <t>國內業務人員</t>
         </is>
       </c>
     </row>
@@ -20247,7 +21114,7 @@
           <t>F508-教育行政儲備幹部(高雄市鳳山區)</t>
         </is>
       </c>
-      <c r="H446" t="inlineStr">
+      <c r="H446" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -20260,6 +21127,11 @@
       <c r="J446" t="inlineStr">
         <is>
           <t>補習班招生人員</t>
+        </is>
+      </c>
+      <c r="M446" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -20439,7 +21311,7 @@
           <t>補習班儲備主管-桃園(起薪$32500+月招生獎金+首年簽約獎金$14000+每年證照獎金$3000)</t>
         </is>
       </c>
-      <c r="H450" t="inlineStr">
+      <c r="H450" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -20450,6 +21322,11 @@
         </is>
       </c>
       <c r="J450" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
+        </is>
+      </c>
+      <c r="M450" s="9" t="inlineStr">
         <is>
           <t>儲備幹部</t>
         </is>
@@ -20487,7 +21364,7 @@
           <t>補習班儲備主管-中壢(起薪$32500+月招生獎金+首年簽約獎金$14000+每年證照獎金$3000)</t>
         </is>
       </c>
-      <c r="H451" t="inlineStr">
+      <c r="H451" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -20498,6 +21375,11 @@
         </is>
       </c>
       <c r="J451" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
+        </is>
+      </c>
+      <c r="M451" s="9" t="inlineStr">
         <is>
           <t>儲備幹部</t>
         </is>
@@ -20535,7 +21417,7 @@
           <t>【資深儲備店長｜營運主管（具管理經驗）】★ 週休二日 ★</t>
         </is>
       </c>
-      <c r="H452" t="inlineStr">
+      <c r="H452" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -20546,6 +21428,11 @@
         </is>
       </c>
       <c r="J452" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
+        </is>
+      </c>
+      <c r="M452" s="9" t="inlineStr">
         <is>
           <t>儲備幹部</t>
         </is>
@@ -20583,7 +21470,7 @@
           <t>【儲備行政客服主管】數位牙體技術行政專員（歡迎牙技背景轉型）</t>
         </is>
       </c>
-      <c r="H453" t="inlineStr">
+      <c r="H453" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -20596,6 +21483,11 @@
       <c r="J453" s="7" t="inlineStr">
         <is>
           <t>業務助理</t>
+        </is>
+      </c>
+      <c r="M453" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -20631,7 +21523,7 @@
           <t>教務行政儲備幹部</t>
         </is>
       </c>
-      <c r="H454" t="inlineStr">
+      <c r="H454" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -20644,6 +21536,11 @@
       <c r="J454" s="7" t="inlineStr">
         <is>
           <t>行政主管</t>
+        </is>
+      </c>
+      <c r="M454" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -20732,7 +21629,7 @@
           <t>《新竹》營運業務助理</t>
         </is>
       </c>
-      <c r="H456" t="inlineStr">
+      <c r="H456" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -20745,6 +21642,11 @@
       <c r="J456" t="inlineStr">
         <is>
           <t>店長／門市管理人員</t>
+        </is>
+      </c>
+      <c r="M456" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -20876,7 +21778,7 @@
           <t>出口專利業務助理</t>
         </is>
       </c>
-      <c r="H459" t="inlineStr">
+      <c r="H459" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -20889,6 +21791,11 @@
       <c r="J459" s="7" t="inlineStr">
         <is>
           <t>英文翻譯／口譯人員</t>
+        </is>
+      </c>
+      <c r="M459" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -20924,9 +21831,14 @@
           <t>行政會計</t>
         </is>
       </c>
-      <c r="H460" t="inlineStr">
+      <c r="H460" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M460" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -21202,7 +22114,7 @@
           <t>儲備幹部</t>
         </is>
       </c>
-      <c r="H466" t="inlineStr">
+      <c r="H466" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -21215,6 +22127,11 @@
       <c r="J466" s="7" t="inlineStr">
         <is>
           <t>採購人員</t>
+        </is>
+      </c>
+      <c r="M466" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -21442,7 +22359,7 @@
           <t>行政會計助理(需具行政經驗三~五年尤佳)</t>
         </is>
       </c>
-      <c r="H471" t="inlineStr">
+      <c r="H471" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -21465,6 +22382,11 @@
       <c r="L471" s="7" t="inlineStr">
         <is>
           <t>業務助理</t>
+        </is>
+      </c>
+      <c r="M471" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -21879,7 +22801,7 @@
           <t>行政秘書與會計</t>
         </is>
       </c>
-      <c r="H480" s="7" t="inlineStr">
+      <c r="H480" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -21892,6 +22814,11 @@
       <c r="J480" t="inlineStr">
         <is>
           <t>秘書</t>
+        </is>
+      </c>
+      <c r="M480" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -21927,7 +22854,7 @@
           <t>儲備人員</t>
         </is>
       </c>
-      <c r="H481" t="inlineStr">
+      <c r="H481" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -21940,6 +22867,11 @@
       <c r="J481" s="7" t="inlineStr">
         <is>
           <t>牙醫助理</t>
+        </is>
+      </c>
+      <c r="M481" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -22091,7 +23023,7 @@
           <t>行政會計助理</t>
         </is>
       </c>
-      <c r="H484" t="inlineStr">
+      <c r="H484" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -22109,6 +23041,11 @@
       <c r="K484" s="7" t="inlineStr">
         <is>
           <t>業務助理</t>
+        </is>
+      </c>
+      <c r="M484" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -22144,7 +23081,7 @@
           <t>業務助理人員/行政助理(桃園) 周休二日、有特休、三節</t>
         </is>
       </c>
-      <c r="H485" s="7" t="inlineStr">
+      <c r="H485" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -22162,6 +23099,11 @@
       <c r="K485" s="7" t="inlineStr">
         <is>
           <t>電話客服人員</t>
+        </is>
+      </c>
+      <c r="M485" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -22425,9 +23367,14 @@
           <t>業務助理(夜校生佳)</t>
         </is>
       </c>
-      <c r="H492" t="inlineStr">
+      <c r="H492" s="8" t="inlineStr">
         <is>
           <t>工讀生</t>
+        </is>
+      </c>
+      <c r="M492" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -22731,7 +23678,7 @@
           <t>工讀儲備美語老師(可接受培訓)(佳音台中東興分校)</t>
         </is>
       </c>
-      <c r="H499" t="inlineStr">
+      <c r="H499" s="8" t="inlineStr">
         <is>
           <t>工讀生</t>
         </is>
@@ -22744,6 +23691,11 @@
       <c r="J499" s="7" t="inlineStr">
         <is>
           <t>升學補習班老師</t>
+        </is>
+      </c>
+      <c r="M499" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -23748,9 +24700,14 @@
           <t>房仲業務助理-游佳諭經理 0938-514-518</t>
         </is>
       </c>
-      <c r="H523" t="inlineStr">
+      <c r="H523" s="8" t="inlineStr">
         <is>
           <t>工讀生</t>
+        </is>
+      </c>
+      <c r="M523" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -23786,9 +24743,14 @@
           <t>澄清平等醫院 環衛儲備幹部</t>
         </is>
       </c>
-      <c r="H524" t="inlineStr">
+      <c r="H524" s="8" t="inlineStr">
         <is>
           <t>工讀生</t>
+        </is>
+      </c>
+      <c r="M524" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -24322,7 +25284,7 @@
           <t>儲備幹部-時薪制帶隊組長(蘆竹區、大園區)</t>
         </is>
       </c>
-      <c r="H536" t="inlineStr">
+      <c r="H536" s="8" t="inlineStr">
         <is>
           <t>工讀生</t>
         </is>
@@ -24335,6 +25297,11 @@
       <c r="J536" s="7" t="inlineStr">
         <is>
           <t>國內業務人員</t>
+        </is>
+      </c>
+      <c r="M536" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -24370,7 +25337,7 @@
           <t>儲備幹部-時薪制帶隊組長(中壢區、平鎮區)</t>
         </is>
       </c>
-      <c r="H537" t="inlineStr">
+      <c r="H537" s="8" t="inlineStr">
         <is>
           <t>工讀生</t>
         </is>
@@ -24383,6 +25350,11 @@
       <c r="J537" s="7" t="inlineStr">
         <is>
           <t>國內業務人員</t>
+        </is>
+      </c>
+      <c r="M537" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -24418,7 +25390,7 @@
           <t>儲備幹部-時薪制帶隊組長(觀音區、新屋區)</t>
         </is>
       </c>
-      <c r="H538" t="inlineStr">
+      <c r="H538" s="8" t="inlineStr">
         <is>
           <t>工讀生</t>
         </is>
@@ -24431,6 +25403,11 @@
       <c r="J538" s="7" t="inlineStr">
         <is>
           <t>國內業務人員</t>
+        </is>
+      </c>
+      <c r="M538" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -24466,7 +25443,7 @@
           <t>儲備幹部-時薪制帶隊組長(桃園區、龜山區)</t>
         </is>
       </c>
-      <c r="H539" t="inlineStr">
+      <c r="H539" s="8" t="inlineStr">
         <is>
           <t>工讀生</t>
         </is>
@@ -24479,6 +25456,11 @@
       <c r="J539" s="7" t="inlineStr">
         <is>
           <t>國內業務人員</t>
+        </is>
+      </c>
+      <c r="M539" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -24562,7 +25544,7 @@
           <t>統一超商中二區會計行政(時薪制)</t>
         </is>
       </c>
-      <c r="H541" t="inlineStr">
+      <c r="H541" s="8" t="inlineStr">
         <is>
           <t>工讀生</t>
         </is>
@@ -24570,6 +25552,11 @@
       <c r="I541" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M541" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -24605,7 +25592,7 @@
           <t>二銷暨藝品儲備幹部</t>
         </is>
       </c>
-      <c r="H542" t="inlineStr">
+      <c r="H542" s="8" t="inlineStr">
         <is>
           <t>工讀生</t>
         </is>
@@ -24613,6 +25600,11 @@
       <c r="I542" s="7" t="inlineStr">
         <is>
           <t>旅遊休閒類主管</t>
+        </is>
+      </c>
+      <c r="M542" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -24648,7 +25640,7 @@
           <t>統一超商中一區會計行政(時薪制)</t>
         </is>
       </c>
-      <c r="H543" t="inlineStr">
+      <c r="H543" s="8" t="inlineStr">
         <is>
           <t>工讀生</t>
         </is>
@@ -24656,6 +25648,11 @@
       <c r="I543" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M543" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -24691,7 +25688,7 @@
           <t>行政業務助理 工讀</t>
         </is>
       </c>
-      <c r="H544" t="inlineStr">
+      <c r="H544" s="8" t="inlineStr">
         <is>
           <t>工讀生</t>
         </is>
@@ -24699,6 +25696,11 @@
       <c r="I544" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M544" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -25814,7 +26816,7 @@
           <t>儲備幹部-時薪制帶隊組長(八德區、中園區)</t>
         </is>
       </c>
-      <c r="H570" t="inlineStr">
+      <c r="H570" s="8" t="inlineStr">
         <is>
           <t>工讀生</t>
         </is>
@@ -25827,6 +26829,11 @@
       <c r="J570" s="7" t="inlineStr">
         <is>
           <t>國內業務人員</t>
+        </is>
+      </c>
+      <c r="M570" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -25862,7 +26869,7 @@
           <t>儲備幹部-時薪制帶隊組長(楊梅區、新豐鄉)</t>
         </is>
       </c>
-      <c r="H571" t="inlineStr">
+      <c r="H571" s="8" t="inlineStr">
         <is>
           <t>工讀生</t>
         </is>
@@ -25875,6 +26882,11 @@
       <c r="J571" s="7" t="inlineStr">
         <is>
           <t>國內業務人員</t>
+        </is>
+      </c>
+      <c r="M571" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -25910,7 +26922,7 @@
           <t>儲備幹部-時薪制帶隊組長(龍潭區、湖口區)</t>
         </is>
       </c>
-      <c r="H572" t="inlineStr">
+      <c r="H572" s="8" t="inlineStr">
         <is>
           <t>工讀生</t>
         </is>
@@ -25923,6 +26935,11 @@
       <c r="J572" s="7" t="inlineStr">
         <is>
           <t>國內業務人員</t>
+        </is>
+      </c>
+      <c r="M572" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -25958,7 +26975,7 @@
           <t>儲備幹部-時薪制帶隊組長(竹東鎮、關西鎮))</t>
         </is>
       </c>
-      <c r="H573" t="inlineStr">
+      <c r="H573" s="8" t="inlineStr">
         <is>
           <t>工讀生</t>
         </is>
@@ -25971,6 +26988,11 @@
       <c r="J573" s="7" t="inlineStr">
         <is>
           <t>國內業務人員</t>
+        </is>
+      </c>
+      <c r="M573" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -27241,7 +28263,7 @@
           <t>儲備幹部-時薪制帶隊組長(台中二區)</t>
         </is>
       </c>
-      <c r="H604" t="inlineStr">
+      <c r="H604" s="8" t="inlineStr">
         <is>
           <t>工讀生</t>
         </is>
@@ -27254,6 +28276,11 @@
       <c r="J604" s="7" t="inlineStr">
         <is>
           <t>國內業務人員</t>
+        </is>
+      </c>
+      <c r="M604" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -27517,7 +28544,7 @@
           <t>工讀/兼職 業務助理</t>
         </is>
       </c>
-      <c r="H611" t="inlineStr">
+      <c r="H611" s="8" t="inlineStr">
         <is>
           <t>工讀生</t>
         </is>
@@ -27525,6 +28552,11 @@
       <c r="I611" s="7" t="inlineStr">
         <is>
           <t>秘書</t>
+        </is>
+      </c>
+      <c r="M611" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -27560,7 +28592,7 @@
           <t>⭐正職好同事在這裡⭐業務助理⭐人資助理⭐招募助理⭐內勤免外出⭐</t>
         </is>
       </c>
-      <c r="H612" t="inlineStr">
+      <c r="H612" s="8" t="inlineStr">
         <is>
           <t>工讀生</t>
         </is>
@@ -27571,6 +28603,11 @@
         </is>
       </c>
       <c r="J612" t="inlineStr">
+        <is>
+          <t>業務助理</t>
+        </is>
+      </c>
+      <c r="M612" s="9" t="inlineStr">
         <is>
           <t>業務助理</t>
         </is>
@@ -29852,7 +30889,7 @@
           <t>兼職護理師</t>
         </is>
       </c>
-      <c r="H661" s="7" t="inlineStr">
+      <c r="H661" s="8" t="inlineStr">
         <is>
           <t>工讀生</t>
         </is>
@@ -29865,6 +30902,11 @@
       <c r="J661" s="7" t="inlineStr">
         <is>
           <t>門市／店員／專櫃人員</t>
+        </is>
+      </c>
+      <c r="M661" s="9" t="inlineStr">
+        <is>
+          <t>護理師</t>
         </is>
       </c>
     </row>
@@ -29900,7 +30942,7 @@
           <t>儲備業務/PM_越南(飛宏科技)</t>
         </is>
       </c>
-      <c r="H662" t="inlineStr">
+      <c r="H662" s="8" t="inlineStr">
         <is>
           <t>工讀生</t>
         </is>
@@ -29908,6 +30950,11 @@
       <c r="I662" s="7" t="inlineStr">
         <is>
           <t>業務助理</t>
+        </is>
+      </c>
+      <c r="M662" s="9" t="inlineStr">
+        <is>
+          <t>產品經理</t>
         </is>
       </c>
     </row>
@@ -30797,7 +31844,7 @@
           <t>儲備採購/人資_越南(飛宏科技)</t>
         </is>
       </c>
-      <c r="H681" t="inlineStr">
+      <c r="H681" s="8" t="inlineStr">
         <is>
           <t>工讀生</t>
         </is>
@@ -30810,6 +31857,11 @@
       <c r="J681" s="7" t="inlineStr">
         <is>
           <t>採購助理</t>
+        </is>
+      </c>
+      <c r="M681" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -31434,7 +32486,7 @@
           <t>【學生實習】2026年中租控股_合迪儲備業務實習</t>
         </is>
       </c>
-      <c r="H695" t="inlineStr">
+      <c r="H695" s="8" t="inlineStr">
         <is>
           <t>工讀生</t>
         </is>
@@ -31447,6 +32499,11 @@
       <c r="J695" s="7" t="inlineStr">
         <is>
           <t>國內業務人員</t>
+        </is>
+      </c>
+      <c r="M695" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -32078,9 +33135,14 @@
           <t>儲備幹部</t>
         </is>
       </c>
-      <c r="H708" s="7" t="inlineStr">
+      <c r="H708" s="8" t="inlineStr">
         <is>
           <t>行政主管</t>
+        </is>
+      </c>
+      <c r="M708" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -32116,9 +33178,14 @@
           <t>『明光義塾-台北大直教室』全職教師/儲備幹部</t>
         </is>
       </c>
-      <c r="H709" s="7" t="inlineStr">
+      <c r="H709" s="8" t="inlineStr">
         <is>
           <t>行政主管</t>
+        </is>
+      </c>
+      <c r="M709" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -32154,7 +33221,7 @@
           <t>管理部儲備主管</t>
         </is>
       </c>
-      <c r="H710" s="7" t="inlineStr">
+      <c r="H710" s="8" t="inlineStr">
         <is>
           <t>行政主管</t>
         </is>
@@ -32162,6 +33229,11 @@
       <c r="I710" t="inlineStr">
         <is>
           <t>經營管理主管</t>
+        </is>
+      </c>
+      <c r="M710" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -32293,7 +33365,7 @@
           <t>總公司：儲備管理經理(Global Mall)</t>
         </is>
       </c>
-      <c r="H713" s="7" t="inlineStr">
+      <c r="H713" s="8" t="inlineStr">
         <is>
           <t>行政主管</t>
         </is>
@@ -32306,6 +33378,11 @@
       <c r="J713" t="inlineStr">
         <is>
           <t>經營管理主管</t>
+        </is>
+      </c>
+      <c r="M713" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -32341,7 +33418,7 @@
           <t>總公司：南區儲備管理經理(Global Mall)</t>
         </is>
       </c>
-      <c r="H714" s="7" t="inlineStr">
+      <c r="H714" s="8" t="inlineStr">
         <is>
           <t>行政主管</t>
         </is>
@@ -32354,6 +33431,11 @@
       <c r="J714" t="inlineStr">
         <is>
           <t>經營管理主管</t>
+        </is>
+      </c>
+      <c r="M714" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -32437,7 +33519,7 @@
           <t>儲備幹部-彰化中心</t>
         </is>
       </c>
-      <c r="H716" s="7" t="inlineStr">
+      <c r="H716" s="8" t="inlineStr">
         <is>
           <t>行政主管</t>
         </is>
@@ -32445,6 +33527,11 @@
       <c r="I716" s="7" t="inlineStr">
         <is>
           <t>護理師</t>
+        </is>
+      </c>
+      <c r="M716" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -32480,7 +33567,7 @@
           <t>儲備幹部-芬園中心</t>
         </is>
       </c>
-      <c r="H717" s="7" t="inlineStr">
+      <c r="H717" s="8" t="inlineStr">
         <is>
           <t>行政主管</t>
         </is>
@@ -32488,6 +33575,11 @@
       <c r="I717" s="7" t="inlineStr">
         <is>
           <t>護理師</t>
+        </is>
+      </c>
+      <c r="M717" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -32523,7 +33615,7 @@
           <t>儲備幹部-伸港中心</t>
         </is>
       </c>
-      <c r="H718" s="7" t="inlineStr">
+      <c r="H718" s="8" t="inlineStr">
         <is>
           <t>行政主管</t>
         </is>
@@ -32531,6 +33623,11 @@
       <c r="I718" s="7" t="inlineStr">
         <is>
           <t>護理師</t>
+        </is>
+      </c>
+      <c r="M718" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -32566,7 +33663,7 @@
           <t>儲備幹部-秀水中心</t>
         </is>
       </c>
-      <c r="H719" s="7" t="inlineStr">
+      <c r="H719" s="8" t="inlineStr">
         <is>
           <t>行政主管</t>
         </is>
@@ -32574,6 +33671,11 @@
       <c r="I719" s="7" t="inlineStr">
         <is>
           <t>護理師</t>
+        </is>
+      </c>
+      <c r="M719" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -32609,7 +33711,7 @@
           <t>明光義塾-全職行政櫃台(儲備幹部)</t>
         </is>
       </c>
-      <c r="H720" s="7" t="inlineStr">
+      <c r="H720" s="8" t="inlineStr">
         <is>
           <t>行政主管</t>
         </is>
@@ -32622,6 +33724,11 @@
       <c r="J720" s="7" t="inlineStr">
         <is>
           <t>教育訓練人員</t>
+        </is>
+      </c>
+      <c r="M720" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -32657,7 +33764,7 @@
           <t>[中雲嘉]台中市 營運儲備幹部</t>
         </is>
       </c>
-      <c r="H721" s="7" t="inlineStr">
+      <c r="H721" s="8" t="inlineStr">
         <is>
           <t>行政主管</t>
         </is>
@@ -32670,6 +33777,11 @@
       <c r="J721" s="7" t="inlineStr">
         <is>
           <t>客服主管</t>
+        </is>
+      </c>
+      <c r="M721" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -32801,7 +33913,7 @@
           <t>展間業務助理</t>
         </is>
       </c>
-      <c r="H724" s="7" t="inlineStr">
+      <c r="H724" s="8" t="inlineStr">
         <is>
           <t>行政主管</t>
         </is>
@@ -32819,6 +33931,11 @@
       <c r="K724" s="7" t="inlineStr">
         <is>
           <t>客服主管</t>
+        </is>
+      </c>
+      <c r="M724" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -32983,9 +34100,14 @@
           <t>行政業務助理</t>
         </is>
       </c>
-      <c r="H728" s="7" t="inlineStr">
+      <c r="H728" s="8" t="inlineStr">
         <is>
           <t>秘書</t>
+        </is>
+      </c>
+      <c r="M728" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -33279,7 +34401,7 @@
           <t>★【行政會計】固定休六日、國定假日、有特休、每月有獎勵機制請見內文</t>
         </is>
       </c>
-      <c r="H735" s="7" t="inlineStr">
+      <c r="H735" s="8" t="inlineStr">
         <is>
           <t>秘書</t>
         </is>
@@ -33292,6 +34414,11 @@
       <c r="J735" t="inlineStr">
         <is>
           <t>電腦操作／資料輸入</t>
+        </is>
+      </c>
+      <c r="M735" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -33471,7 +34598,7 @@
           <t>業務助理 (月薪3萬4千元起，熟電腦文書.表現優良三個月後再調薪6千元~9千元.應徵請洽 黃小姐0930-367-292 )</t>
         </is>
       </c>
-      <c r="H739" s="7" t="inlineStr">
+      <c r="H739" s="8" t="inlineStr">
         <is>
           <t>秘書</t>
         </is>
@@ -33484,6 +34611,11 @@
       <c r="J739" t="inlineStr">
         <is>
           <t>特別助理</t>
+        </is>
+      </c>
+      <c r="M739" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -33663,7 +34795,7 @@
           <t>禾馨醫療【民權內科】業務助理(健檢服務)(可培養業務、個案管理能力)</t>
         </is>
       </c>
-      <c r="H743" s="7" t="inlineStr">
+      <c r="H743" s="8" t="inlineStr">
         <is>
           <t>秘書</t>
         </is>
@@ -33676,6 +34808,11 @@
       <c r="J743" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M743" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -33893,7 +35030,7 @@
           <t>行政業務助理</t>
         </is>
       </c>
-      <c r="H748" s="7" t="inlineStr">
+      <c r="H748" s="8" t="inlineStr">
         <is>
           <t>秘書</t>
         </is>
@@ -33906,6 +35043,11 @@
       <c r="J748" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M748" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -34755,7 +35897,7 @@
           <t>董事長特助兼會計助理</t>
         </is>
       </c>
-      <c r="H767" s="7" t="inlineStr">
+      <c r="H767" s="8" t="inlineStr">
         <is>
           <t>秘書</t>
         </is>
@@ -34763,6 +35905,11 @@
       <c r="I767" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M767" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -35402,7 +36549,7 @@
           <t>＜住商士北科加盟店＞業務助理</t>
         </is>
       </c>
-      <c r="H781" s="7" t="inlineStr">
+      <c r="H781" s="8" t="inlineStr">
         <is>
           <t>秘書</t>
         </is>
@@ -35415,6 +36562,11 @@
       <c r="J781" t="inlineStr">
         <is>
           <t>不動產經紀人／營業員</t>
+        </is>
+      </c>
+      <c r="M781" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -35450,7 +36602,7 @@
           <t>業務助理</t>
         </is>
       </c>
-      <c r="H782" s="7" t="inlineStr">
+      <c r="H782" s="8" t="inlineStr">
         <is>
           <t>秘書</t>
         </is>
@@ -35463,6 +36615,11 @@
       <c r="J782" t="inlineStr">
         <is>
           <t>不動產經紀人／營業員</t>
+        </is>
+      </c>
+      <c r="M782" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -35498,7 +36655,7 @@
           <t>業務助理（行政內勤）※意者請洽劉經理0915-787-987</t>
         </is>
       </c>
-      <c r="H783" s="7" t="inlineStr">
+      <c r="H783" s="8" t="inlineStr">
         <is>
           <t>秘書</t>
         </is>
@@ -35511,6 +36668,11 @@
       <c r="J783" t="inlineStr">
         <is>
           <t>工讀生</t>
+        </is>
+      </c>
+      <c r="M783" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -35546,7 +36708,7 @@
           <t>房仲業務助理(長期工讀) ※意者請洽鍾經理0981-816-111</t>
         </is>
       </c>
-      <c r="H784" s="7" t="inlineStr">
+      <c r="H784" s="8" t="inlineStr">
         <is>
           <t>秘書</t>
         </is>
@@ -35559,6 +36721,11 @@
       <c r="J784" t="inlineStr">
         <is>
           <t>工讀生</t>
+        </is>
+      </c>
+      <c r="M784" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -35746,9 +36913,14 @@
           <t>行政業務助理</t>
         </is>
       </c>
-      <c r="H789" s="7" t="inlineStr">
+      <c r="H789" s="8" t="inlineStr">
         <is>
           <t>秘書</t>
+        </is>
+      </c>
+      <c r="M789" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -35784,7 +36956,7 @@
           <t>儲備專案管理人員</t>
         </is>
       </c>
-      <c r="H790" s="7" t="inlineStr">
+      <c r="H790" s="8" t="inlineStr">
         <is>
           <t>秘書</t>
         </is>
@@ -35797,6 +36969,11 @@
       <c r="J790" s="7" t="inlineStr">
         <is>
           <t>國貿人員</t>
+        </is>
+      </c>
+      <c r="M790" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -35880,7 +37057,7 @@
           <t>會計行政人員</t>
         </is>
       </c>
-      <c r="H792" s="7" t="inlineStr">
+      <c r="H792" s="8" t="inlineStr">
         <is>
           <t>秘書</t>
         </is>
@@ -35893,6 +37070,11 @@
       <c r="J792" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M792" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -35928,7 +37110,7 @@
           <t>業務助理</t>
         </is>
       </c>
-      <c r="H793" s="7" t="inlineStr">
+      <c r="H793" s="8" t="inlineStr">
         <is>
           <t>秘書</t>
         </is>
@@ -35941,6 +37123,11 @@
       <c r="J793" s="7" t="inlineStr">
         <is>
           <t>社群經營人員</t>
+        </is>
+      </c>
+      <c r="M793" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -36168,7 +37355,7 @@
           <t>頭份市#住商不動產-頭份昌隆店業務助理</t>
         </is>
       </c>
-      <c r="H798" s="7" t="inlineStr">
+      <c r="H798" s="8" t="inlineStr">
         <is>
           <t>秘書</t>
         </is>
@@ -36181,6 +37368,11 @@
       <c r="J798" t="inlineStr">
         <is>
           <t>電腦操作／資料輸入</t>
+        </is>
+      </c>
+      <c r="M798" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -36552,7 +37744,7 @@
           <t>業務助理</t>
         </is>
       </c>
-      <c r="H806" t="inlineStr">
+      <c r="H806" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -36560,6 +37752,11 @@
       <c r="I806" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M806" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -36595,7 +37792,7 @@
           <t>業務助理</t>
         </is>
       </c>
-      <c r="H807" t="inlineStr">
+      <c r="H807" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -36603,6 +37800,11 @@
       <c r="I807" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M807" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -36638,7 +37840,7 @@
           <t>行政/業務助理(中壢)</t>
         </is>
       </c>
-      <c r="H808" t="inlineStr">
+      <c r="H808" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -36646,6 +37848,11 @@
       <c r="I808" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M808" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -36858,9 +38065,14 @@
           <t>業務助理</t>
         </is>
       </c>
-      <c r="H813" t="inlineStr">
+      <c r="H813" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M813" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -36896,9 +38108,14 @@
           <t>稽查人員〈需外勤〉-儲備幹部</t>
         </is>
       </c>
-      <c r="H814" t="inlineStr">
+      <c r="H814" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M814" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -36934,9 +38151,14 @@
           <t>埔里元首館-會計助理</t>
         </is>
       </c>
-      <c r="H815" t="inlineStr">
+      <c r="H815" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M815" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -36972,9 +38194,14 @@
           <t>業務助理人員</t>
         </is>
       </c>
-      <c r="H816" t="inlineStr">
+      <c r="H816" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M816" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -37091,9 +38318,14 @@
           <t>長照專車業務助理</t>
         </is>
       </c>
-      <c r="H819" t="inlineStr">
+      <c r="H819" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M819" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -37167,9 +38399,14 @@
           <t>工程業務助理</t>
         </is>
       </c>
-      <c r="H821" t="inlineStr">
+      <c r="H821" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M821" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -37291,7 +38528,7 @@
           <t>行政會計人員</t>
         </is>
       </c>
-      <c r="H824" t="inlineStr">
+      <c r="H824" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -37304,6 +38541,11 @@
       <c r="J824" s="7" t="inlineStr">
         <is>
           <t>業務助理</t>
+        </is>
+      </c>
+      <c r="M824" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -37339,7 +38581,7 @@
           <t>業務助理(台中)</t>
         </is>
       </c>
-      <c r="H825" t="inlineStr">
+      <c r="H825" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -37352,6 +38594,11 @@
       <c r="J825" t="inlineStr">
         <is>
           <t>電腦操作／資料輸入</t>
+        </is>
+      </c>
+      <c r="M825" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -37660,7 +38907,7 @@
           <t>行政會計</t>
         </is>
       </c>
-      <c r="H832" t="inlineStr">
+      <c r="H832" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -37668,6 +38915,11 @@
       <c r="I832" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M832" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -37746,7 +38998,7 @@
           <t>業務會計助理</t>
         </is>
       </c>
-      <c r="H834" t="inlineStr">
+      <c r="H834" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -37754,6 +39006,11 @@
       <c r="I834" s="7" t="inlineStr">
         <is>
           <t>業務助理</t>
+        </is>
+      </c>
+      <c r="M834" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -38019,7 +39276,7 @@
           <t>不動產業務助理</t>
         </is>
       </c>
-      <c r="H840" t="inlineStr">
+      <c r="H840" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -38032,6 +39289,11 @@
       <c r="J840" s="7" t="inlineStr">
         <is>
           <t>秘書</t>
+        </is>
+      </c>
+      <c r="M840" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -38158,7 +39420,7 @@
           <t>業務助理 (新建築工務部)</t>
         </is>
       </c>
-      <c r="H843" t="inlineStr">
+      <c r="H843" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -38166,6 +39428,11 @@
       <c r="I843" s="7" t="inlineStr">
         <is>
           <t>工務助理</t>
+        </is>
+      </c>
+      <c r="M843" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -38353,7 +39620,7 @@
           <t>行政業務助理</t>
         </is>
       </c>
-      <c r="H848" t="inlineStr">
+      <c r="H848" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -38366,6 +39633,11 @@
       <c r="J848" s="7" t="inlineStr">
         <is>
           <t>行銷企劃助理</t>
+        </is>
+      </c>
+      <c r="M848" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -38401,7 +39673,7 @@
           <t>工研院產科國際所_業務暨客服助理派遣人員(Q200)_台北、新竹皆可</t>
         </is>
       </c>
-      <c r="H849" t="inlineStr">
+      <c r="H849" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -38414,6 +39686,11 @@
       <c r="J849" s="7" t="inlineStr">
         <is>
           <t>研究助理</t>
+        </is>
+      </c>
+      <c r="M849" s="9" t="inlineStr">
+        <is>
+          <t>客服人員</t>
         </is>
       </c>
     </row>
@@ -38487,7 +39764,7 @@
           <t>護理系：約聘教學助理(具護理師證照)</t>
         </is>
       </c>
-      <c r="H851" s="7" t="inlineStr">
+      <c r="H851" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -38495,6 +39772,11 @@
       <c r="I851" s="7" t="inlineStr">
         <is>
           <t>其他研究人員</t>
+        </is>
+      </c>
+      <c r="M851" s="9" t="inlineStr">
+        <is>
+          <t>護理師</t>
         </is>
       </c>
     </row>
@@ -38568,9 +39850,14 @@
           <t>業務助理</t>
         </is>
       </c>
-      <c r="H853" t="inlineStr">
+      <c r="H853" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M853" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -38606,7 +39893,7 @@
           <t>(儲備人員)行政人員</t>
         </is>
       </c>
-      <c r="H854" t="inlineStr">
+      <c r="H854" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -38619,6 +39906,11 @@
       <c r="J854" s="7" t="inlineStr">
         <is>
           <t>行銷企劃人員</t>
+        </is>
+      </c>
+      <c r="M854" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -38869,9 +40161,14 @@
           <t>業務助理</t>
         </is>
       </c>
-      <c r="H860" t="inlineStr">
+      <c r="H860" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M860" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -38907,9 +40204,14 @@
           <t>行政業務助理</t>
         </is>
       </c>
-      <c r="H861" t="inlineStr">
+      <c r="H861" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M861" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -38993,7 +40295,7 @@
           <t>(桃園門市)門市業務助理</t>
         </is>
       </c>
-      <c r="H863" t="inlineStr">
+      <c r="H863" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -39006,6 +40308,11 @@
       <c r="J863" s="7" t="inlineStr">
         <is>
           <t>財務／會計助理</t>
+        </is>
+      </c>
+      <c r="M863" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -39041,7 +40348,7 @@
           <t>業務助理/儲備電商業務</t>
         </is>
       </c>
-      <c r="H864" t="inlineStr">
+      <c r="H864" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -39054,6 +40361,11 @@
       <c r="J864" s="7" t="inlineStr">
         <is>
           <t>客服人員</t>
+        </is>
+      </c>
+      <c r="M864" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -39089,7 +40401,7 @@
           <t>會計助理</t>
         </is>
       </c>
-      <c r="H865" t="inlineStr">
+      <c r="H865" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -39102,6 +40414,11 @@
       <c r="J865" s="7" t="inlineStr">
         <is>
           <t>秘書</t>
+        </is>
+      </c>
+      <c r="M865" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -39306,7 +40623,7 @@
           <t>會計室暨技術合作處誠徵約聘計畫助理</t>
         </is>
       </c>
-      <c r="H870" t="inlineStr">
+      <c r="H870" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -39314,6 +40631,11 @@
       <c r="I870" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M870" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -39349,7 +40671,7 @@
           <t>幼教行銷處業務助理-新北</t>
         </is>
       </c>
-      <c r="H871" t="inlineStr">
+      <c r="H871" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -39357,6 +40679,11 @@
       <c r="I871" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M871" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -39814,7 +41141,7 @@
           <t>(南港區)行政業務助理</t>
         </is>
       </c>
-      <c r="H881" t="inlineStr">
+      <c r="H881" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -39827,6 +41154,11 @@
       <c r="J881" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M881" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -39862,7 +41194,7 @@
           <t>國土署-都市更新會計助理(派駐內政部國土管理署(財務管理科))</t>
         </is>
       </c>
-      <c r="H882" t="inlineStr">
+      <c r="H882" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -39875,6 +41207,11 @@
       <c r="J882" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M882" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -39958,7 +41295,7 @@
           <t>高雄市岡山區行政會計</t>
         </is>
       </c>
-      <c r="H884" t="inlineStr">
+      <c r="H884" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -39971,6 +41308,11 @@
       <c r="J884" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M884" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -40054,7 +41396,7 @@
           <t>行政會計/櫃台內勤/儲備幹部</t>
         </is>
       </c>
-      <c r="H886" t="inlineStr">
+      <c r="H886" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -40067,6 +41409,11 @@
       <c r="J886" s="7" t="inlineStr">
         <is>
           <t>財務／會計助理</t>
+        </is>
+      </c>
+      <c r="M886" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -40102,7 +41449,7 @@
           <t>倉管儲備幹部</t>
         </is>
       </c>
-      <c r="H887" t="inlineStr">
+      <c r="H887" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -40115,6 +41462,11 @@
       <c r="J887" s="7" t="inlineStr">
         <is>
           <t>倉儲物流人員</t>
+        </is>
+      </c>
+      <c r="M887" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -40150,7 +41502,7 @@
           <t>▶業務助理(嘉義住商檜意村加盟店)</t>
         </is>
       </c>
-      <c r="H888" t="inlineStr">
+      <c r="H888" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -40163,6 +41515,11 @@
       <c r="J888" s="7" t="inlineStr">
         <is>
           <t>秘書</t>
+        </is>
+      </c>
+      <c r="M888" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -40198,7 +41555,7 @@
           <t>●業務助理(嘉義檜意村加盟店)●</t>
         </is>
       </c>
-      <c r="H889" t="inlineStr">
+      <c r="H889" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -40211,6 +41568,11 @@
       <c r="J889" s="7" t="inlineStr">
         <is>
           <t>秘書</t>
+        </is>
+      </c>
+      <c r="M889" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -40246,7 +41608,7 @@
           <t>~業務助理(嘉義檜意村加盟店)~</t>
         </is>
       </c>
-      <c r="H890" t="inlineStr">
+      <c r="H890" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -40259,6 +41621,11 @@
       <c r="J890" s="7" t="inlineStr">
         <is>
           <t>秘書</t>
+        </is>
+      </c>
+      <c r="M890" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -40390,7 +41757,7 @@
           <t>業務助理</t>
         </is>
       </c>
-      <c r="H893" t="inlineStr">
+      <c r="H893" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -40403,6 +41770,11 @@
       <c r="J893" t="inlineStr">
         <is>
           <t>秘書</t>
+        </is>
+      </c>
+      <c r="M893" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -40438,7 +41810,7 @@
           <t>儲備行政職【電話客服】｜國際企業｜月薪32,000｜訂單處理🅙➊➏</t>
         </is>
       </c>
-      <c r="H894" t="inlineStr">
+      <c r="H894" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -40451,6 +41823,11 @@
       <c r="J894" t="inlineStr">
         <is>
           <t>電話客服人員</t>
+        </is>
+      </c>
+      <c r="M894" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -40774,7 +42151,7 @@
           <t>業務助理</t>
         </is>
       </c>
-      <c r="H901" t="inlineStr">
+      <c r="H901" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -40787,6 +42164,11 @@
       <c r="J901" s="7" t="inlineStr">
         <is>
           <t>國貿助理</t>
+        </is>
+      </c>
+      <c r="M901" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -40918,7 +42300,7 @@
           <t>尹浤國貿社｜行政業務助理／網站管理／行政跟單助理</t>
         </is>
       </c>
-      <c r="H904" t="inlineStr">
+      <c r="H904" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -40931,6 +42313,11 @@
       <c r="J904" t="inlineStr">
         <is>
           <t>特別助理</t>
+        </is>
+      </c>
+      <c r="M904" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -41350,7 +42737,7 @@
           <t>塑膠部-會計人員(伸港地區)</t>
         </is>
       </c>
-      <c r="H913" t="inlineStr">
+      <c r="H913" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -41363,6 +42750,11 @@
       <c r="J913" s="7" t="inlineStr">
         <is>
           <t>廠務助理</t>
+        </is>
+      </c>
+      <c r="M913" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -41398,7 +42790,7 @@
           <t>擴大徵才~【五結廠】生產儲備幹部</t>
         </is>
       </c>
-      <c r="H914" t="inlineStr">
+      <c r="H914" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -41411,6 +42803,11 @@
       <c r="J914" t="inlineStr">
         <is>
           <t>倉管／物料管理員</t>
+        </is>
+      </c>
+      <c r="M914" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -41494,7 +42891,7 @@
           <t>禾馨醫療【士林產後護理之家】倉管兼院區助理</t>
         </is>
       </c>
-      <c r="H916" s="7" t="inlineStr">
+      <c r="H916" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -41505,6 +42902,11 @@
         </is>
       </c>
       <c r="J916" t="inlineStr">
+        <is>
+          <t>倉管／物料管理員</t>
+        </is>
+      </c>
+      <c r="M916" s="9" t="inlineStr">
         <is>
           <t>倉管／物料管理員</t>
         </is>
@@ -41686,7 +43088,7 @@
           <t>業務助理</t>
         </is>
       </c>
-      <c r="H920" t="inlineStr">
+      <c r="H920" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -41699,6 +43101,11 @@
       <c r="J920" t="inlineStr">
         <is>
           <t>電腦操作／資料輸入</t>
+        </is>
+      </c>
+      <c r="M920" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -41782,7 +43189,7 @@
           <t>行政業務助理(短期)</t>
         </is>
       </c>
-      <c r="H922" t="inlineStr">
+      <c r="H922" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -41795,6 +43202,11 @@
       <c r="J922" t="inlineStr">
         <is>
           <t>電腦操作／資料輸入</t>
+        </is>
+      </c>
+      <c r="M922" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -41911,7 +43323,7 @@
           <t>業務助理</t>
         </is>
       </c>
-      <c r="H925" t="inlineStr">
+      <c r="H925" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -41924,6 +43336,11 @@
       <c r="J925" s="7" t="inlineStr">
         <is>
           <t>檔案資料管理人員</t>
+        </is>
+      </c>
+      <c r="M925" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -41959,7 +43376,7 @@
           <t>業務助理</t>
         </is>
       </c>
-      <c r="H926" t="inlineStr">
+      <c r="H926" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -41967,6 +43384,11 @@
       <c r="I926" t="inlineStr">
         <is>
           <t>電腦操作／資料輸入</t>
+        </is>
+      </c>
+      <c r="M926" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -42045,7 +43467,7 @@
           <t>業務助理</t>
         </is>
       </c>
-      <c r="H928" t="inlineStr">
+      <c r="H928" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -42058,6 +43480,11 @@
       <c r="J928" s="7" t="inlineStr">
         <is>
           <t>檔案資料管理人員</t>
+        </is>
+      </c>
+      <c r="M928" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -42136,7 +43563,7 @@
           <t>📌誠徵業務助理（歡迎社會新鮮人）</t>
         </is>
       </c>
-      <c r="H930" t="inlineStr">
+      <c r="H930" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -42149,6 +43576,11 @@
       <c r="J930" s="7" t="inlineStr">
         <is>
           <t>美編人員</t>
+        </is>
+      </c>
+      <c r="M930" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -42227,7 +43659,7 @@
           <t>業務助理</t>
         </is>
       </c>
-      <c r="H932" t="inlineStr">
+      <c r="H932" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -42240,6 +43672,11 @@
       <c r="J932" s="7" t="inlineStr">
         <is>
           <t>策展人員</t>
+        </is>
+      </c>
+      <c r="M932" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -42447,7 +43884,7 @@
           <t>業務助理-W1</t>
         </is>
       </c>
-      <c r="H937" t="inlineStr">
+      <c r="H937" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -42455,6 +43892,11 @@
       <c r="I937" s="7" t="inlineStr">
         <is>
           <t>工程助理</t>
+        </is>
+      </c>
+      <c r="M937" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -42528,7 +43970,7 @@
           <t>行政會計助理</t>
         </is>
       </c>
-      <c r="H939" t="inlineStr">
+      <c r="H939" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -42541,6 +43983,11 @@
       <c r="J939" t="inlineStr">
         <is>
           <t>秘書</t>
+        </is>
+      </c>
+      <c r="M939" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -42624,7 +44071,7 @@
           <t>【金融周邊機構，近台北車站】聯徵中心-會計行政人員(歡迎夜校生、在學學生)</t>
         </is>
       </c>
-      <c r="H941" s="7" t="inlineStr">
+      <c r="H941" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -42637,6 +44084,11 @@
       <c r="J941" t="inlineStr">
         <is>
           <t>工讀生</t>
+        </is>
+      </c>
+      <c r="M941" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -42786,9 +44238,14 @@
           <t>派駐政府機構業務人員</t>
         </is>
       </c>
-      <c r="H945" t="inlineStr">
+      <c r="H945" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M945" s="9" t="inlineStr">
+        <is>
+          <t>國內業務人員</t>
         </is>
       </c>
     </row>
@@ -42824,7 +44281,7 @@
           <t>行政/會計助理【桃園地區】</t>
         </is>
       </c>
-      <c r="H946" t="inlineStr">
+      <c r="H946" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -42837,6 +44294,11 @@
       <c r="J946" s="7" t="inlineStr">
         <is>
           <t>總務人員</t>
+        </is>
+      </c>
+      <c r="M946" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -42968,7 +44430,7 @@
           <t>行政業務助理</t>
         </is>
       </c>
-      <c r="H949" t="inlineStr">
+      <c r="H949" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -42981,6 +44443,11 @@
       <c r="J949" s="7" t="inlineStr">
         <is>
           <t>門市／店員／專櫃人員</t>
+        </is>
+      </c>
+      <c r="M949" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -43016,7 +44483,7 @@
           <t>【徵】會計助理兼門市收銀(薪:$32000-$33000)</t>
         </is>
       </c>
-      <c r="H950" t="inlineStr">
+      <c r="H950" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -43029,6 +44496,11 @@
       <c r="J950" t="inlineStr">
         <is>
           <t>售票／收銀人員</t>
+        </is>
+      </c>
+      <c r="M950" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -43064,7 +44536,7 @@
           <t>行政會計儲備幹部 洽高總監0986727619</t>
         </is>
       </c>
-      <c r="H951" t="inlineStr">
+      <c r="H951" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -43077,6 +44549,11 @@
       <c r="J951" s="7" t="inlineStr">
         <is>
           <t>客服人員</t>
+        </is>
+      </c>
+      <c r="M951" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -43112,7 +44589,7 @@
           <t>生管儲備幹部(員林廠)</t>
         </is>
       </c>
-      <c r="H952" t="inlineStr">
+      <c r="H952" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -43125,6 +44602,11 @@
       <c r="J952" s="7" t="inlineStr">
         <is>
           <t>廠務</t>
+        </is>
+      </c>
+      <c r="M952" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -43208,7 +44690,7 @@
           <t>業務助理(高雄)</t>
         </is>
       </c>
-      <c r="H954" t="inlineStr">
+      <c r="H954" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -43221,6 +44703,11 @@
       <c r="J954" s="7" t="inlineStr">
         <is>
           <t>產品管理師</t>
+        </is>
+      </c>
+      <c r="M954" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -43256,7 +44743,7 @@
           <t>【徵】會計美工助理兼收銀人員(33000~35000)</t>
         </is>
       </c>
-      <c r="H955" s="7" t="inlineStr">
+      <c r="H955" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -43269,6 +44756,11 @@
       <c r="J955" s="7" t="inlineStr">
         <is>
           <t>廣告文案企劃人員</t>
+        </is>
+      </c>
+      <c r="M955" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -43352,7 +44844,7 @@
           <t>【徵】會計美工及會計助理(33000~35000)</t>
         </is>
       </c>
-      <c r="H957" t="inlineStr">
+      <c r="H957" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -43365,6 +44857,11 @@
       <c r="J957" s="7" t="inlineStr">
         <is>
           <t>廣告文案企劃人員</t>
+        </is>
+      </c>
+      <c r="M957" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -43496,7 +44993,7 @@
           <t>業務助理</t>
         </is>
       </c>
-      <c r="H960" t="inlineStr">
+      <c r="H960" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -43509,6 +45006,11 @@
       <c r="J960" t="inlineStr">
         <is>
           <t>總務人員</t>
+        </is>
+      </c>
+      <c r="M960" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -43630,7 +45132,7 @@
           <t>【南京店】店務行政會計</t>
         </is>
       </c>
-      <c r="H963" t="inlineStr">
+      <c r="H963" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -43638,6 +45140,11 @@
       <c r="I963" t="inlineStr">
         <is>
           <t>總機／接待／櫃檯人員</t>
+        </is>
+      </c>
+      <c r="M963" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -43716,7 +45223,7 @@
           <t>美業招募/人資/行政/客服/櫃台/10–17</t>
         </is>
       </c>
-      <c r="H965" t="inlineStr">
+      <c r="H965" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -43724,6 +45231,11 @@
       <c r="I965" t="inlineStr">
         <is>
           <t>總機／接待／櫃檯人員</t>
+        </is>
+      </c>
+      <c r="M965" s="9" t="inlineStr">
+        <is>
+          <t>客服人員</t>
         </is>
       </c>
     </row>
@@ -44173,7 +45685,7 @@
           <t>儲備行政主管(近捷運西湖站)(薪水14個月)</t>
         </is>
       </c>
-      <c r="H974" t="inlineStr">
+      <c r="H974" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -44196,6 +45708,11 @@
       <c r="L974" t="inlineStr">
         <is>
           <t>秘書</t>
+        </is>
+      </c>
+      <c r="M974" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -44289,7 +45806,7 @@
           <t>國外經理助理(儲備幹部)-越南(熟倉儲相關)</t>
         </is>
       </c>
-      <c r="H976" s="7" t="inlineStr">
+      <c r="H976" s="8" t="inlineStr">
         <is>
           <t>總務主管</t>
         </is>
@@ -44312,6 +45829,11 @@
       <c r="L976" s="7" t="inlineStr">
         <is>
           <t>財務／會計助理</t>
+        </is>
+      </c>
+      <c r="M976" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -44347,7 +45869,7 @@
           <t>西屯校區-儲備總務主任</t>
         </is>
       </c>
-      <c r="H977" t="inlineStr">
+      <c r="H977" s="8" t="inlineStr">
         <is>
           <t>總務主管</t>
         </is>
@@ -44355,6 +45877,11 @@
       <c r="I977" t="inlineStr">
         <is>
           <t>總務人員</t>
+        </is>
+      </c>
+      <c r="M977" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -44390,7 +45917,7 @@
           <t>總務行政儲備主管</t>
         </is>
       </c>
-      <c r="H978" s="7" t="inlineStr">
+      <c r="H978" s="8" t="inlineStr">
         <is>
           <t>總務主管</t>
         </is>
@@ -44403,6 +45930,11 @@
       <c r="J978" t="inlineStr">
         <is>
           <t>總務人員</t>
+        </is>
+      </c>
+      <c r="M978" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -44562,7 +46094,7 @@
           <t>「客家文化中心」儲備組員（正取1名，備取若干名）</t>
         </is>
       </c>
-      <c r="H982" s="7" t="inlineStr">
+      <c r="H982" s="8" t="inlineStr">
         <is>
           <t>總務人員</t>
         </is>
@@ -44575,6 +46107,11 @@
       <c r="J982" s="7" t="inlineStr">
         <is>
           <t>行銷企劃人員</t>
+        </is>
+      </c>
+      <c r="M982" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -44658,7 +46195,7 @@
           <t>會計助理人員</t>
         </is>
       </c>
-      <c r="H984" s="7" t="inlineStr">
+      <c r="H984" s="8" t="inlineStr">
         <is>
           <t>總務人員</t>
         </is>
@@ -44671,6 +46208,11 @@
       <c r="J984" t="inlineStr">
         <is>
           <t>總機／接待／櫃檯人員</t>
+        </is>
+      </c>
+      <c r="M984" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -44921,7 +46463,7 @@
           <t>儲備幹部</t>
         </is>
       </c>
-      <c r="H990" s="7" t="inlineStr">
+      <c r="H990" s="8" t="inlineStr">
         <is>
           <t>總務人員</t>
         </is>
@@ -44934,6 +46476,11 @@
       <c r="J990" s="7" t="inlineStr">
         <is>
           <t>行政主管</t>
+        </is>
+      </c>
+      <c r="M990" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -44969,7 +46516,7 @@
           <t>會計人員</t>
         </is>
       </c>
-      <c r="H991" s="7" t="inlineStr">
+      <c r="H991" s="8" t="inlineStr">
         <is>
           <t>總務人員</t>
         </is>
@@ -44982,6 +46529,11 @@
       <c r="J991" s="7" t="inlineStr">
         <is>
           <t>業務助理</t>
+        </is>
+      </c>
+      <c r="M991" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -45156,7 +46708,7 @@
           <t>總務儲備專員</t>
         </is>
       </c>
-      <c r="H995" t="inlineStr">
+      <c r="H995" s="8" t="inlineStr">
         <is>
           <t>總務人員</t>
         </is>
@@ -45169,6 +46721,11 @@
       <c r="J995" s="7" t="inlineStr">
         <is>
           <t>採購助理</t>
+        </is>
+      </c>
+      <c r="M995" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -45318,7 +46875,7 @@
           <t>總務儲備主管</t>
         </is>
       </c>
-      <c r="H999" t="inlineStr">
+      <c r="H999" s="8" t="inlineStr">
         <is>
           <t>總務人員</t>
         </is>
@@ -45341,6 +46898,11 @@
       <c r="L999" s="7" t="inlineStr">
         <is>
           <t>職業安全衛生管理人員</t>
+        </is>
+      </c>
+      <c r="M999" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -45376,7 +46938,7 @@
           <t>業務助理</t>
         </is>
       </c>
-      <c r="H1000" s="7" t="inlineStr">
+      <c r="H1000" s="8" t="inlineStr">
         <is>
           <t>總務人員</t>
         </is>
@@ -45399,6 +46961,11 @@
       <c r="L1000" s="7" t="inlineStr">
         <is>
           <t>設計助理</t>
+        </is>
+      </c>
+      <c r="M1000" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -45434,9 +47001,14 @@
           <t>總部_總務高階主管司機</t>
         </is>
       </c>
-      <c r="H1001" s="7" t="inlineStr">
+      <c r="H1001" s="8" t="inlineStr">
         <is>
           <t>總務人員</t>
+        </is>
+      </c>
+      <c r="M1001" s="9" t="inlineStr">
+        <is>
+          <t>主管駕駛</t>
         </is>
       </c>
     </row>
@@ -45472,9 +47044,14 @@
           <t>總務室-專員(環安衛業務主管)</t>
         </is>
       </c>
-      <c r="H1002" s="7" t="inlineStr">
+      <c r="H1002" s="8" t="inlineStr">
         <is>
           <t>總務人員</t>
+        </is>
+      </c>
+      <c r="M1002" s="9" t="inlineStr">
+        <is>
+          <t>國內業務主管</t>
         </is>
       </c>
     </row>
@@ -45639,7 +47216,7 @@
           <t>DS-雙北內勤行政多缺!!!歡迎投遞討論【外商日用品企業_行政助理、業務助理、櫃台行政】</t>
         </is>
       </c>
-      <c r="H1006" s="7" t="inlineStr">
+      <c r="H1006" s="8" t="inlineStr">
         <is>
           <t>總務人員</t>
         </is>
@@ -45652,6 +47229,11 @@
       <c r="J1006" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M1006" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -45687,7 +47269,7 @@
           <t>副主任儲備幹部(總務部)</t>
         </is>
       </c>
-      <c r="H1007" s="7" t="inlineStr">
+      <c r="H1007" s="8" t="inlineStr">
         <is>
           <t>總務人員</t>
         </is>
@@ -45710,6 +47292,11 @@
       <c r="L1007" s="7" t="inlineStr">
         <is>
           <t>教育訓練人員</t>
+        </is>
+      </c>
+      <c r="M1007" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -45841,9 +47428,14 @@
           <t>BEING fit 櫃檯客服(台中歐風門市)</t>
         </is>
       </c>
-      <c r="H1010" s="7" t="inlineStr">
+      <c r="H1010" s="8" t="inlineStr">
         <is>
           <t>總機／接待／櫃檯人員</t>
+        </is>
+      </c>
+      <c r="M1010" s="9" t="inlineStr">
+        <is>
+          <t>客服人員</t>
         </is>
       </c>
     </row>
@@ -46099,7 +47691,7 @@
           <t>行政會計</t>
         </is>
       </c>
-      <c r="H1016" t="inlineStr">
+      <c r="H1016" s="8" t="inlineStr">
         <is>
           <t>總機／接待／櫃檯人員</t>
         </is>
@@ -46107,6 +47699,11 @@
       <c r="I1016" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M1016" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -46271,7 +47868,7 @@
           <t>銀行融資貸款 業務助理（無經驗可）</t>
         </is>
       </c>
-      <c r="H1020" t="inlineStr">
+      <c r="H1020" s="8" t="inlineStr">
         <is>
           <t>總機／接待／櫃檯人員</t>
         </is>
@@ -46284,6 +47881,11 @@
       <c r="J1020" t="inlineStr">
         <is>
           <t>電話行銷人員</t>
+        </is>
+      </c>
+      <c r="M1020" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -46602,7 +48204,7 @@
           <t>會計助理（行政人員）</t>
         </is>
       </c>
-      <c r="H1027" s="7" t="inlineStr">
+      <c r="H1027" s="8" t="inlineStr">
         <is>
           <t>總機／接待／櫃檯人員</t>
         </is>
@@ -46615,6 +48217,11 @@
       <c r="J1027" s="7" t="inlineStr">
         <is>
           <t>客服人員</t>
+        </is>
+      </c>
+      <c r="M1027" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -46827,7 +48434,7 @@
           <t>補習班儲備幹部</t>
         </is>
       </c>
-      <c r="H1032" t="inlineStr">
+      <c r="H1032" s="8" t="inlineStr">
         <is>
           <t>總機／接待／櫃檯人員</t>
         </is>
@@ -46840,6 +48447,11 @@
       <c r="J1032" t="inlineStr">
         <is>
           <t>補習班招生人員</t>
+        </is>
+      </c>
+      <c r="M1032" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -46971,7 +48583,7 @@
           <t>好寶貝產後護理之家–客服專員</t>
         </is>
       </c>
-      <c r="H1035" t="inlineStr">
+      <c r="H1035" s="8" t="inlineStr">
         <is>
           <t>總機／接待／櫃檯人員</t>
         </is>
@@ -46984,6 +48596,11 @@
       <c r="J1035" s="7" t="inlineStr">
         <is>
           <t>門市／店員／專櫃人員</t>
+        </is>
+      </c>
+      <c r="M1035" s="9" t="inlineStr">
+        <is>
+          <t>客服人員</t>
         </is>
       </c>
     </row>
@@ -47115,7 +48732,7 @@
           <t>【儲備店長｜營運主管培訓（無經驗可）】★ 週休二日 ★</t>
         </is>
       </c>
-      <c r="H1038" t="inlineStr">
+      <c r="H1038" s="8" t="inlineStr">
         <is>
           <t>總機／接待／櫃檯人員</t>
         </is>
@@ -47128,6 +48745,11 @@
       <c r="J1038" s="7" t="inlineStr">
         <is>
           <t>店長／門市管理人員</t>
+        </is>
+      </c>
+      <c r="M1038" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -47163,7 +48785,7 @@
           <t>禾馨醫療【士林產後護理之家】客服人員/營銷人員</t>
         </is>
       </c>
-      <c r="H1039" t="inlineStr">
+      <c r="H1039" s="8" t="inlineStr">
         <is>
           <t>總機／接待／櫃檯人員</t>
         </is>
@@ -47176,6 +48798,11 @@
       <c r="J1039" s="7" t="inlineStr">
         <is>
           <t>醫院行政管理人員</t>
+        </is>
+      </c>
+      <c r="M1039" s="9" t="inlineStr">
+        <is>
+          <t>客服人員</t>
         </is>
       </c>
     </row>
@@ -47211,7 +48838,7 @@
           <t>儲備店長</t>
         </is>
       </c>
-      <c r="H1040" t="inlineStr">
+      <c r="H1040" s="8" t="inlineStr">
         <is>
           <t>總機／接待／櫃檯人員</t>
         </is>
@@ -47224,6 +48851,11 @@
       <c r="J1040" s="7" t="inlineStr">
         <is>
           <t>餐飲服務人員</t>
+        </is>
+      </c>
+      <c r="M1040" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -47355,7 +48987,7 @@
           <t>儲備幹部</t>
         </is>
       </c>
-      <c r="H1043" t="inlineStr">
+      <c r="H1043" s="8" t="inlineStr">
         <is>
           <t>總機／接待／櫃檯人員</t>
         </is>
@@ -47373,6 +49005,11 @@
       <c r="K1043" s="7" t="inlineStr">
         <is>
           <t>門市／店員／專櫃人員</t>
+        </is>
+      </c>
+      <c r="M1043" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -47519,7 +49156,7 @@
           <t>(經營管理類)-人資/福委(會計)專員-總公司</t>
         </is>
       </c>
-      <c r="H1046" t="inlineStr">
+      <c r="H1046" s="8" t="inlineStr">
         <is>
           <t>總機／接待／櫃檯人員</t>
         </is>
@@ -47530,6 +49167,11 @@
         </is>
       </c>
       <c r="J1046" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
+        </is>
+      </c>
+      <c r="M1046" s="9" t="inlineStr">
         <is>
           <t>會計／出納／記帳人員</t>
         </is>
@@ -47567,7 +49209,7 @@
           <t>物業管理部 儲備幹部</t>
         </is>
       </c>
-      <c r="H1047" t="inlineStr">
+      <c r="H1047" s="8" t="inlineStr">
         <is>
           <t>總機／接待／櫃檯人員</t>
         </is>
@@ -47580,6 +49222,11 @@
       <c r="J1047" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M1047" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -47615,7 +49262,7 @@
           <t>【國泰集團】客服專員/物業管理儲備幹部</t>
         </is>
       </c>
-      <c r="H1048" t="inlineStr">
+      <c r="H1048" s="8" t="inlineStr">
         <is>
           <t>總機／接待／櫃檯人員</t>
         </is>
@@ -47628,6 +49275,11 @@
       <c r="J1048" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M1048" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -47855,7 +49507,7 @@
           <t>業務助理</t>
         </is>
       </c>
-      <c r="H1053" s="7" t="inlineStr">
+      <c r="H1053" s="8" t="inlineStr">
         <is>
           <t>檔案資料管理人員</t>
         </is>
@@ -47868,6 +49520,11 @@
       <c r="J1053" t="inlineStr">
         <is>
           <t>電腦操作／資料輸入</t>
+        </is>
+      </c>
+      <c r="M1053" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -48186,7 +49843,7 @@
           <t>行政會計《台南》</t>
         </is>
       </c>
-      <c r="H1060" t="inlineStr">
+      <c r="H1060" s="8" t="inlineStr">
         <is>
           <t>電腦操作／資料輸入</t>
         </is>
@@ -48199,6 +49856,11 @@
       <c r="J1060" t="inlineStr">
         <is>
           <t>倉管／物料管理員</t>
+        </is>
+      </c>
+      <c r="M1060" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -48330,7 +49992,7 @@
           <t>兼職行政會計人員</t>
         </is>
       </c>
-      <c r="H1063" t="inlineStr">
+      <c r="H1063" s="8" t="inlineStr">
         <is>
           <t>電腦操作／資料輸入</t>
         </is>
@@ -48343,6 +50005,11 @@
       <c r="J1063" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M1063" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -48378,7 +50045,7 @@
           <t>財務會計內勤工讀生（排班彈性／無經驗可、手把手教學／冷氣辦公室環境單純）</t>
         </is>
       </c>
-      <c r="H1064" t="inlineStr">
+      <c r="H1064" s="8" t="inlineStr">
         <is>
           <t>電腦操作／資料輸入</t>
         </is>
@@ -48391,6 +50058,11 @@
       <c r="J1064" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M1064" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -48426,7 +50098,7 @@
           <t>會計助理</t>
         </is>
       </c>
-      <c r="H1065" t="inlineStr">
+      <c r="H1065" s="8" t="inlineStr">
         <is>
           <t>電腦操作／資料輸入</t>
         </is>
@@ -48439,6 +50111,11 @@
       <c r="J1065" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M1065" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -48575,7 +50252,7 @@
           <t>承鑫車業｜門市行政會計</t>
         </is>
       </c>
-      <c r="H1068" s="7" t="inlineStr">
+      <c r="H1068" s="8" t="inlineStr">
         <is>
           <t>電腦操作／資料輸入</t>
         </is>
@@ -48588,6 +50265,11 @@
       <c r="J1068" s="7" t="inlineStr">
         <is>
           <t>總機／接待／櫃檯人員</t>
+        </is>
+      </c>
+      <c r="M1068" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -48762,9 +50444,14 @@
           <t>【全職】藥局門市倉儲人員／行政文書助理（月薪40,000 - 42,000+伙食津貼+年終）</t>
         </is>
       </c>
-      <c r="H1072" s="7" t="inlineStr">
+      <c r="H1072" s="8" t="inlineStr">
         <is>
           <t>電腦操作／資料輸入</t>
+        </is>
+      </c>
+      <c r="M1072" s="9" t="inlineStr">
+        <is>
+          <t>倉管／物料管理員</t>
         </is>
       </c>
     </row>
@@ -48817,7 +50504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L199"/>
+  <dimension ref="A1:M199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -48903,6 +50590,11 @@
           <t>現有5</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>建議1</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -48936,7 +50628,7 @@
           <t>業務助理</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="H2" s="8" t="inlineStr">
         <is>
           <t>儲備幹部</t>
         </is>
@@ -48944,6 +50636,11 @@
       <c r="I2" s="7" t="inlineStr">
         <is>
           <t>基層管理幹部</t>
+        </is>
+      </c>
+      <c r="M2" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -49285,7 +50982,7 @@
           <t>行政管理儲備幹部</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>人事／人力資源專員</t>
         </is>
@@ -49298,6 +50995,11 @@
       <c r="J10" s="7" t="inlineStr">
         <is>
           <t>行政主管</t>
+        </is>
+      </c>
+      <c r="M10" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -49457,9 +51159,14 @@
           <t>儲備幹部</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>人力／外勞仲介</t>
+        </is>
+      </c>
+      <c r="M14" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -49495,9 +51202,14 @@
           <t>業務人員-中壢</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>人力／外勞仲介</t>
+        </is>
+      </c>
+      <c r="M15" s="9" t="inlineStr">
+        <is>
+          <t>國內業務人員</t>
         </is>
       </c>
     </row>
@@ -49614,7 +51326,7 @@
           <t>總部-早午餐培訓儲備主管【需出差、具備餐飲管理經驗】台北/需自備車輛</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>教育訓練人員</t>
         </is>
@@ -49627,6 +51339,11 @@
       <c r="J18" t="inlineStr">
         <is>
           <t>餐飲服務人員</t>
+        </is>
+      </c>
+      <c r="M18" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -49662,7 +51379,7 @@
           <t>總部-早午餐培訓儲備主管【需出差、具備餐飲管理經驗】桃園/需自備車輛</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>教育訓練人員</t>
         </is>
@@ -49675,6 +51392,11 @@
       <c r="J19" t="inlineStr">
         <is>
           <t>餐飲服務人員</t>
+        </is>
+      </c>
+      <c r="M19" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -49710,7 +51432,7 @@
           <t>總部-早午餐培訓儲備主管【需出差、具備餐飲管理經驗】台南</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>教育訓練人員</t>
         </is>
@@ -49718,6 +51440,11 @@
       <c r="I20" t="inlineStr">
         <is>
           <t>餐飲主管</t>
+        </is>
+      </c>
+      <c r="M20" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -49935,7 +51662,7 @@
           <t>【上市建材】教育訓練管理師/專員(海外業務管理部) 《享年終績效與季度分紅獎金》</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>教育訓練人員</t>
         </is>
@@ -49948,6 +51675,11 @@
       <c r="J25" s="7" t="inlineStr">
         <is>
           <t>國貿助理</t>
+        </is>
+      </c>
+      <c r="M25" s="9" t="inlineStr">
+        <is>
+          <t>國外業務人員</t>
         </is>
       </c>
     </row>
@@ -50112,7 +51844,7 @@
           <t>聖約翰科技大學【徵聘儲備人員】徵聘約計畫及約聘行政人員數名</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>人事助理</t>
         </is>
@@ -50125,6 +51857,11 @@
       <c r="J29" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M29" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -50208,7 +51945,7 @@
           <t>人資總務助理</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31" s="8" t="inlineStr">
         <is>
           <t>人事助理</t>
         </is>
@@ -50219,6 +51956,11 @@
         </is>
       </c>
       <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>總務人員</t>
+        </is>
+      </c>
+      <c r="M31" s="9" t="inlineStr">
         <is>
           <t>總務人員</t>
         </is>
@@ -50256,9 +51998,14 @@
           <t>【2026鴻海集團-AI雲端實習生】CESBG專區-人資實習生-教育訓練</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32" s="8" t="inlineStr">
         <is>
           <t>人事助理</t>
+        </is>
+      </c>
+      <c r="M32" s="9" t="inlineStr">
+        <is>
+          <t>教育訓練人員</t>
         </is>
       </c>
     </row>
@@ -50408,12 +52155,17 @@
           <t>人資總務部 助理</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H36" s="8" t="inlineStr">
         <is>
           <t>人事助理</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>總務人員</t>
+        </is>
+      </c>
+      <c r="M36" s="9" t="inlineStr">
         <is>
           <t>總務人員</t>
         </is>
@@ -50618,9 +52370,14 @@
           <t>健檢課-業務專員</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H41" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M41" s="9" t="inlineStr">
+        <is>
+          <t>國內業務人員</t>
         </is>
       </c>
     </row>
@@ -50775,9 +52532,14 @@
           <t>行政儲備幹部（機料部）</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H45" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M45" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -50942,7 +52704,7 @@
           <t>行政助理(儲備幹部)</t>
         </is>
       </c>
-      <c r="H49" s="7" t="inlineStr">
+      <c r="H49" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -50955,6 +52717,11 @@
       <c r="J49" t="inlineStr">
         <is>
           <t>電腦操作／資料輸入</t>
+        </is>
+      </c>
+      <c r="M49" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -50990,7 +52757,7 @@
           <t>【外商】生管業務助理（契約）</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H50" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -50998,6 +52765,11 @@
       <c r="I50" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M50" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -51129,7 +52901,7 @@
           <t>【外貿協會】專案經理(創新業務中心/產業創新組)</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H53" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -51142,6 +52914,11 @@
       <c r="J53" t="inlineStr">
         <is>
           <t>其他專案管理師</t>
+        </is>
+      </c>
+      <c r="M53" s="9" t="inlineStr">
+        <is>
+          <t>專案經理</t>
         </is>
       </c>
     </row>
@@ -51225,7 +53002,7 @@
           <t>老鷹地產中信房屋會計</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H55" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -51233,6 +53010,11 @@
       <c r="I55" s="7" t="inlineStr">
         <is>
           <t>秘書</t>
+        </is>
+      </c>
+      <c r="M55" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -51455,7 +53237,7 @@
           <t>房仲店頭-業務助理</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="H60" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -51468,6 +53250,11 @@
       <c r="J60" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M60" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -51675,7 +53462,7 @@
           <t>事務員(健檢課)-具備會計背景</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H65" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -51683,6 +53470,11 @@
       <c r="I65" s="7" t="inlineStr">
         <is>
           <t>醫院行政管理人員</t>
+        </is>
+      </c>
+      <c r="M65" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -51756,12 +53548,17 @@
           <t>DAYOU 大祐珠寶招募門市業務助理</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="H67" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
+        <is>
+          <t>業務助理</t>
+        </is>
+      </c>
+      <c r="M67" s="9" t="inlineStr">
         <is>
           <t>業務助理</t>
         </is>
@@ -51880,12 +53677,17 @@
           <t>業務會計人員</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H70" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
+        </is>
+      </c>
+      <c r="M70" s="9" t="inlineStr">
         <is>
           <t>會計／出納／記帳人員</t>
         </is>
@@ -52019,7 +53821,7 @@
           <t>業務主管助理</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="H73" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -52032,6 +53834,11 @@
       <c r="J73" t="inlineStr">
         <is>
           <t>特別助理</t>
+        </is>
+      </c>
+      <c r="M73" s="9" t="inlineStr">
+        <is>
+          <t>國內業務主管</t>
         </is>
       </c>
     </row>
@@ -52067,7 +53874,7 @@
           <t>倉管儲備人員</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H74" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -52080,6 +53887,11 @@
       <c r="J74" s="7" t="inlineStr">
         <is>
           <t>理貨人員</t>
+        </is>
+      </c>
+      <c r="M74" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -52259,7 +54071,7 @@
           <t>儲備教保員</t>
         </is>
       </c>
-      <c r="H78" s="7" t="inlineStr">
+      <c r="H78" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -52272,6 +54084,11 @@
       <c r="J78" t="inlineStr">
         <is>
           <t>幼教老師</t>
+        </is>
+      </c>
+      <c r="M78" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -52307,7 +54124,7 @@
           <t>廠務管理儲備幹部</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="H79" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -52320,6 +54137,11 @@
       <c r="J79" t="inlineStr">
         <is>
           <t>領班／管理幹部</t>
+        </is>
+      </c>
+      <c r="M79" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -52355,7 +54177,7 @@
           <t>監理所業務人員(台北信義區)</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="H80" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -52368,6 +54190,11 @@
       <c r="J80" s="7" t="inlineStr">
         <is>
           <t>小客車／小貨車司機</t>
+        </is>
+      </c>
+      <c r="M80" s="9" t="inlineStr">
+        <is>
+          <t>國內業務人員</t>
         </is>
       </c>
     </row>
@@ -52499,7 +54326,7 @@
           <t>【資深儲備店長｜營運主管（具管理經驗）】★ 週休二日 ★</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="H83" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -52510,6 +54337,11 @@
         </is>
       </c>
       <c r="J83" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
+        </is>
+      </c>
+      <c r="M83" s="9" t="inlineStr">
         <is>
           <t>儲備幹部</t>
         </is>
@@ -52547,7 +54379,7 @@
           <t>《新竹》營運業務助理</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="H84" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -52560,6 +54392,11 @@
       <c r="J84" t="inlineStr">
         <is>
           <t>店長／門市管理人員</t>
+        </is>
+      </c>
+      <c r="M84" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -52595,7 +54432,7 @@
           <t>出口專利業務助理</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="H85" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -52608,6 +54445,11 @@
       <c r="J85" s="7" t="inlineStr">
         <is>
           <t>英文翻譯／口譯人員</t>
+        </is>
+      </c>
+      <c r="M85" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -52643,7 +54485,7 @@
           <t>儲備幹部</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="H86" s="8" t="inlineStr">
         <is>
           <t>行政人員</t>
         </is>
@@ -52656,6 +54498,11 @@
       <c r="J86" s="7" t="inlineStr">
         <is>
           <t>採購人員</t>
+        </is>
+      </c>
+      <c r="M86" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -54516,7 +56363,7 @@
           <t>【學生實習】2026年中租控股_合迪儲備業務實習</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
+      <c r="H127" s="8" t="inlineStr">
         <is>
           <t>工讀生</t>
         </is>
@@ -54529,6 +56376,11 @@
       <c r="J127" s="7" t="inlineStr">
         <is>
           <t>國內業務人員</t>
+        </is>
+      </c>
+      <c r="M127" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -54612,9 +56464,14 @@
           <t>『明光義塾-台北大直教室』全職教師/儲備幹部</t>
         </is>
       </c>
-      <c r="H129" s="7" t="inlineStr">
+      <c r="H129" s="8" t="inlineStr">
         <is>
           <t>行政主管</t>
+        </is>
+      </c>
+      <c r="M129" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -54698,7 +56555,7 @@
           <t>★【行政會計】固定休六日、國定假日、有特休、每月有獎勵機制請見內文</t>
         </is>
       </c>
-      <c r="H131" s="7" t="inlineStr">
+      <c r="H131" s="8" t="inlineStr">
         <is>
           <t>秘書</t>
         </is>
@@ -54711,6 +56568,11 @@
       <c r="J131" t="inlineStr">
         <is>
           <t>電腦操作／資料輸入</t>
+        </is>
+      </c>
+      <c r="M131" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -54923,9 +56785,14 @@
           <t>行政業務助理</t>
         </is>
       </c>
-      <c r="H136" s="7" t="inlineStr">
+      <c r="H136" s="8" t="inlineStr">
         <is>
           <t>秘書</t>
+        </is>
+      </c>
+      <c r="M136" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -55153,7 +57020,7 @@
           <t>業務助理</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
+      <c r="H141" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -55161,6 +57028,11 @@
       <c r="I141" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M141" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -55196,7 +57068,7 @@
           <t>業務助理</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
+      <c r="H142" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -55204,6 +57076,11 @@
       <c r="I142" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M142" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -55239,9 +57116,14 @@
           <t>稽查人員〈需外勤〉-儲備幹部</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
+      <c r="H143" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M143" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -55277,9 +57159,14 @@
           <t>長照專車業務助理</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
+      <c r="H144" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M144" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -55406,7 +57293,7 @@
           <t>行政會計</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
+      <c r="H147" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -55414,6 +57301,11 @@
       <c r="I147" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M147" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -55492,7 +57384,7 @@
           <t>業務會計助理</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
+      <c r="H149" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -55500,6 +57392,11 @@
       <c r="I149" s="7" t="inlineStr">
         <is>
           <t>業務助理</t>
+        </is>
+      </c>
+      <c r="M149" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -55611,7 +57508,7 @@
           <t>工研院產科國際所_業務暨客服助理派遣人員(Q200)_台北、新竹皆可</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
+      <c r="H152" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -55624,6 +57521,11 @@
       <c r="J152" s="7" t="inlineStr">
         <is>
           <t>研究助理</t>
+        </is>
+      </c>
+      <c r="M152" s="9" t="inlineStr">
+        <is>
+          <t>客服人員</t>
         </is>
       </c>
     </row>
@@ -55659,7 +57561,7 @@
           <t>護理系：約聘教學助理(具護理師證照)</t>
         </is>
       </c>
-      <c r="H153" s="7" t="inlineStr">
+      <c r="H153" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -55667,6 +57569,11 @@
       <c r="I153" s="7" t="inlineStr">
         <is>
           <t>其他研究人員</t>
+        </is>
+      </c>
+      <c r="M153" s="9" t="inlineStr">
+        <is>
+          <t>護理師</t>
         </is>
       </c>
     </row>
@@ -55884,7 +57791,7 @@
           <t>國土署-都市更新會計助理(派駐內政部國土管理署(財務管理科))</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
+      <c r="H158" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -55897,6 +57804,11 @@
       <c r="J158" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M158" s="9" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
         </is>
       </c>
     </row>
@@ -56124,7 +58036,7 @@
           <t>儲備行政職【電話客服】｜國際企業｜月薪32,000｜訂單處理🅙➊➏</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
+      <c r="H163" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -56137,6 +58049,11 @@
       <c r="J163" t="inlineStr">
         <is>
           <t>電話客服人員</t>
+        </is>
+      </c>
+      <c r="M163" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -56258,7 +58175,7 @@
           <t>業務助理</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
+      <c r="H166" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -56266,6 +58183,11 @@
       <c r="I166" t="inlineStr">
         <is>
           <t>電腦操作／資料輸入</t>
+        </is>
+      </c>
+      <c r="M166" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
@@ -56339,9 +58261,14 @@
           <t>派駐政府機構業務人員</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
+      <c r="H168" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
+        </is>
+      </c>
+      <c r="M168" s="9" t="inlineStr">
+        <is>
+          <t>國內業務人員</t>
         </is>
       </c>
     </row>
@@ -56377,7 +58304,7 @@
           <t>美業招募/人資/行政/客服/櫃台/10–17</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
+      <c r="H169" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -56385,6 +58312,11 @@
       <c r="I169" t="inlineStr">
         <is>
           <t>總機／接待／櫃檯人員</t>
+        </is>
+      </c>
+      <c r="M169" s="9" t="inlineStr">
+        <is>
+          <t>客服人員</t>
         </is>
       </c>
     </row>
@@ -56420,7 +58352,7 @@
           <t>儲備行政主管(近捷運西湖站)(薪水14個月)</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
+      <c r="H170" s="8" t="inlineStr">
         <is>
           <t>行政助理</t>
         </is>
@@ -56443,6 +58375,11 @@
       <c r="L170" t="inlineStr">
         <is>
           <t>秘書</t>
+        </is>
+      </c>
+      <c r="M170" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -56723,7 +58660,7 @@
           <t>總務儲備專員</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
+      <c r="H176" s="8" t="inlineStr">
         <is>
           <t>總務人員</t>
         </is>
@@ -56736,6 +58673,11 @@
       <c r="J176" s="7" t="inlineStr">
         <is>
           <t>採購助理</t>
+        </is>
+      </c>
+      <c r="M176" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -56771,9 +58713,14 @@
           <t>總部_總務高階主管司機</t>
         </is>
       </c>
-      <c r="H177" s="7" t="inlineStr">
+      <c r="H177" s="8" t="inlineStr">
         <is>
           <t>總務人員</t>
+        </is>
+      </c>
+      <c r="M177" s="9" t="inlineStr">
+        <is>
+          <t>主管駕駛</t>
         </is>
       </c>
     </row>
@@ -56900,9 +58847,14 @@
           <t>BEING fit 櫃檯客服(台中歐風門市)</t>
         </is>
       </c>
-      <c r="H180" s="7" t="inlineStr">
+      <c r="H180" s="8" t="inlineStr">
         <is>
           <t>總機／接待／櫃檯人員</t>
+        </is>
+      </c>
+      <c r="M180" s="9" t="inlineStr">
+        <is>
+          <t>客服人員</t>
         </is>
       </c>
     </row>
@@ -57130,7 +59082,7 @@
           <t>補習班儲備幹部</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
+      <c r="H185" s="8" t="inlineStr">
         <is>
           <t>總機／接待／櫃檯人員</t>
         </is>
@@ -57143,6 +59095,11 @@
       <c r="J185" t="inlineStr">
         <is>
           <t>補習班招生人員</t>
+        </is>
+      </c>
+      <c r="M185" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -57322,7 +59279,7 @@
           <t>【儲備店長｜營運主管培訓（無經驗可）】★ 週休二日 ★</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
+      <c r="H189" s="8" t="inlineStr">
         <is>
           <t>總機／接待／櫃檯人員</t>
         </is>
@@ -57335,6 +59292,11 @@
       <c r="J189" s="7" t="inlineStr">
         <is>
           <t>店長／門市管理人員</t>
+        </is>
+      </c>
+      <c r="M189" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -57428,7 +59390,7 @@
           <t>(經營管理類)-人資/福委(會計)專員-總公司</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
+      <c r="H191" s="8" t="inlineStr">
         <is>
           <t>總機／接待／櫃檯人員</t>
         </is>
@@ -57439,6 +59401,11 @@
         </is>
       </c>
       <c r="J191" t="inlineStr">
+        <is>
+          <t>會計／出納／記帳人員</t>
+        </is>
+      </c>
+      <c r="M191" s="9" t="inlineStr">
         <is>
           <t>會計／出納／記帳人員</t>
         </is>
@@ -57476,7 +59443,7 @@
           <t>物業管理部 儲備幹部</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
+      <c r="H192" s="8" t="inlineStr">
         <is>
           <t>總機／接待／櫃檯人員</t>
         </is>
@@ -57489,6 +59456,11 @@
       <c r="J192" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M192" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -57524,7 +59496,7 @@
           <t>【國泰集團】客服專員/物業管理儲備幹部</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
+      <c r="H193" s="8" t="inlineStr">
         <is>
           <t>總機／接待／櫃檯人員</t>
         </is>
@@ -57537,6 +59509,11 @@
       <c r="J193" t="inlineStr">
         <is>
           <t>行政人員</t>
+        </is>
+      </c>
+      <c r="M193" s="9" t="inlineStr">
+        <is>
+          <t>儲備幹部</t>
         </is>
       </c>
     </row>
@@ -57572,7 +59549,7 @@
           <t>業務助理</t>
         </is>
       </c>
-      <c r="H194" s="7" t="inlineStr">
+      <c r="H194" s="8" t="inlineStr">
         <is>
           <t>檔案資料管理人員</t>
         </is>
@@ -57585,6 +59562,11 @@
       <c r="J194" t="inlineStr">
         <is>
           <t>電腦操作／資料輸入</t>
+        </is>
+      </c>
+      <c r="M194" s="9" t="inlineStr">
+        <is>
+          <t>業務助理</t>
         </is>
       </c>
     </row>
